--- a/data/Locations.xlsx
+++ b/data/Locations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\landscapingUOB-api\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E5B1A2E-5A24-401C-A2D6-EA83994DD2ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98D4AEE-B9BD-48DF-9BC7-7CE0E90A0793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="162">
   <si>
     <t>Location type</t>
   </si>
@@ -182,9 +182,6 @@
     <t>Deanship of Admission &amp; Registration</t>
   </si>
   <si>
-    <t>https://i.postimg.cc/MT3Ywv7H/S37-1.jpg</t>
-  </si>
-  <si>
     <t>S38</t>
   </si>
   <si>
@@ -368,9 +365,6 @@
     <t>Mosque</t>
   </si>
   <si>
-    <t>https://i.postimg.cc/G2PN8NJ4/Buildings-image.png</t>
-  </si>
-  <si>
     <t>Infrastructure</t>
   </si>
   <si>
@@ -380,9 +374,6 @@
     <t>Boundary Wall</t>
   </si>
   <si>
-    <t>https://i.postimg.cc/bwr6y42y/Boundary-wall.jpg</t>
-  </si>
-  <si>
     <t>Facilities</t>
   </si>
   <si>
@@ -462,6 +453,75 @@
   </si>
   <si>
     <t>https://i.postimg.cc/PJXwkWyR/In_front_of_S45_7.jpg</t>
+  </si>
+  <si>
+    <t>Image 4</t>
+  </si>
+  <si>
+    <t>Image 5</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/L6603kBS/S17-4.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/wTTbQ5c3/S17-3.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/vHHSt7LT/S17-2.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/YqqyzNfH/S17-area3.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/DzVk693V/DSC-0114.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/FH3Yqd05/S1A-4.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/RFQ8bRZQ/S1B-2.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/cH4j23t0/S2-Surroundings-4.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/TwYSFb5G/S2-Surroundings-2.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/V6sVVmqm/infrastructure.png</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/4xgyHSvr/S6.png</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/wBVctNSJ/S22-6.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/Jh1YdRm7/S37-6.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/25z9XCmk/S37.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/nL0RyNcb/S37-1.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/ZKWWpNyg/S38-3.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/9FDDZ9qn/S38-6-(1).jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/59hX50q1/S39-5.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/v8J47BLy/S39-7.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/xjwXGCy2/S39-5-(1).jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/wxC15vc6/S39-3.jpg</t>
   </si>
 </sst>
 </file>
@@ -854,7 +914,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.90625" customWidth="1"/>
@@ -862,17 +922,19 @@
     <col min="3" max="3" width="53.36328125" customWidth="1"/>
     <col min="4" max="4" width="46.453125" style="4" customWidth="1"/>
     <col min="5" max="5" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="44.36328125" customWidth="1"/>
-    <col min="7" max="7" width="45.1796875" customWidth="1"/>
-    <col min="8" max="8" width="46" customWidth="1"/>
+    <col min="6" max="6" width="41.90625" customWidth="1"/>
+    <col min="7" max="7" width="44.81640625" customWidth="1"/>
+    <col min="8" max="8" width="46.1796875" customWidth="1"/>
+    <col min="9" max="9" width="38.36328125" customWidth="1"/>
+    <col min="10" max="10" width="38.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
@@ -881,19 +943,25 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -909,8 +977,23 @@
       <c r="E2">
         <v>699</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F2" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="J2" s="13" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -926,8 +1009,14 @@
       <c r="E3">
         <v>600</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F3" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -943,8 +1032,14 @@
       <c r="E4">
         <v>350</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F4" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -960,8 +1055,14 @@
       <c r="E5">
         <v>186</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F5" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -977,8 +1078,17 @@
       <c r="E6">
         <v>77</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F6" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -994,8 +1104,11 @@
       <c r="E7">
         <v>330</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F7" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1011,8 +1124,11 @@
       <c r="E8">
         <v>280</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F8" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1028,8 +1144,11 @@
       <c r="E9">
         <v>270</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F9" s="13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1045,8 +1164,11 @@
       <c r="E10">
         <v>120</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F10" s="13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1062,8 +1184,14 @@
       <c r="E11">
         <v>440</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F11" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1079,8 +1207,11 @@
       <c r="E12">
         <v>105</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F12" s="13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1096,8 +1227,11 @@
       <c r="E13">
         <v>1050</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F13" s="13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1113,8 +1247,11 @@
       <c r="E14">
         <v>80</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F14" s="13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -1130,8 +1267,11 @@
       <c r="E15">
         <v>145</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F15" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -1142,285 +1282,318 @@
         <v>47</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>48</v>
+        <v>153</v>
       </c>
       <c r="E16">
         <v>1350</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F16" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>3</v>
       </c>
       <c r="B17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" t="s">
         <v>49</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" s="5" t="s">
         <v>50</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>51</v>
       </c>
       <c r="E17">
         <v>175</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F17" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>3</v>
       </c>
       <c r="B18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" t="s">
         <v>52</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" s="5" t="s">
         <v>53</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>54</v>
       </c>
       <c r="E18">
         <v>1000</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="F18" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="J18" s="13" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
         <v>3</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="D19" s="8" t="s">
         <v>56</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>57</v>
       </c>
       <c r="E19" s="7">
         <v>1000</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>3</v>
       </c>
       <c r="B20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" t="s">
         <v>58</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" s="5" t="s">
         <v>59</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>60</v>
       </c>
       <c r="E20">
         <v>350</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>3</v>
       </c>
       <c r="B21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" t="s">
         <v>61</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="E21">
         <v>464</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>3</v>
       </c>
       <c r="B22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" t="s">
         <v>64</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>66</v>
       </c>
       <c r="E22">
         <v>310</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>3</v>
       </c>
       <c r="B23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" t="s">
         <v>67</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="E23">
         <v>195</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>3</v>
       </c>
       <c r="B24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" t="s">
         <v>70</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" s="5" t="s">
         <v>71</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>72</v>
       </c>
       <c r="E24">
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>3</v>
       </c>
       <c r="B25" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" t="s">
         <v>73</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" s="5" t="s">
         <v>74</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>75</v>
       </c>
       <c r="E25">
         <v>180</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>3</v>
       </c>
       <c r="B26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" t="s">
         <v>76</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>78</v>
       </c>
       <c r="E26">
         <v>90</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>3</v>
       </c>
       <c r="B27" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27" t="s">
         <v>79</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>81</v>
       </c>
       <c r="E27">
         <v>150</v>
       </c>
     </row>
-    <row r="28" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
         <v>3</v>
       </c>
       <c r="B28" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="D28" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D28" s="8" t="s">
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>3</v>
-      </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>85</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" s="5" t="s">
         <v>86</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>87</v>
       </c>
       <c r="E29">
         <v>399</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>3</v>
       </c>
       <c r="B30" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" t="s">
         <v>88</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>90</v>
       </c>
       <c r="E30">
         <v>163</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>3</v>
       </c>
       <c r="B31" t="s">
+        <v>90</v>
+      </c>
+      <c r="C31" t="s">
         <v>91</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>93</v>
       </c>
       <c r="E31">
         <v>194</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>3</v>
       </c>
       <c r="B32" t="s">
+        <v>93</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="D32" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>96</v>
       </c>
       <c r="E32">
         <v>373</v>
@@ -1431,13 +1604,13 @@
         <v>3</v>
       </c>
       <c r="B33" t="s">
+        <v>96</v>
+      </c>
+      <c r="C33" t="s">
+        <v>88</v>
+      </c>
+      <c r="D33" s="5" t="s">
         <v>97</v>
-      </c>
-      <c r="C33" t="s">
-        <v>89</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>98</v>
       </c>
       <c r="E33">
         <v>161</v>
@@ -1448,13 +1621,13 @@
         <v>3</v>
       </c>
       <c r="B34" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="D34" s="8" t="s">
         <v>100</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>101</v>
       </c>
       <c r="E34" s="7">
         <v>600</v>
@@ -1465,13 +1638,13 @@
         <v>3</v>
       </c>
       <c r="B35" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="D35" s="8" t="s">
         <v>103</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>104</v>
       </c>
       <c r="E35" s="7">
         <v>205</v>
@@ -1482,13 +1655,13 @@
         <v>3</v>
       </c>
       <c r="B36" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C36" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="D36" s="8" t="s">
         <v>106</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>107</v>
       </c>
       <c r="E36" s="7">
         <v>205</v>
@@ -1499,13 +1672,13 @@
         <v>3</v>
       </c>
       <c r="B37" t="s">
+        <v>107</v>
+      </c>
+      <c r="C37" t="s">
         <v>108</v>
       </c>
-      <c r="C37" t="s">
-        <v>109</v>
-      </c>
       <c r="D37" s="5" t="s">
-        <v>110</v>
+        <v>151</v>
       </c>
       <c r="E37">
         <v>350</v>
@@ -1513,16 +1686,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C38" t="s">
         <v>111</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C38" t="s">
-        <v>113</v>
-      </c>
       <c r="D38" s="5" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
       <c r="E38">
         <v>142</v>
@@ -1530,13 +1703,13 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B39" t="s">
         <v>10</v>
       </c>
       <c r="C39" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D39" s="9"/>
       <c r="E39">
@@ -1545,16 +1718,16 @@
     </row>
     <row r="40" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A40" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D40" s="8" t="s">
         <v>115</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>118</v>
       </c>
       <c r="E40" s="7">
         <v>600</v>
@@ -1562,16 +1735,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
+        <v>116</v>
+      </c>
+      <c r="B41" t="s">
+        <v>117</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D41" s="5" t="s">
         <v>119</v>
-      </c>
-      <c r="B41" t="s">
-        <v>120</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>122</v>
       </c>
       <c r="E41">
         <v>5300</v>
@@ -1579,16 +1752,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B42" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C42" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E42">
         <v>16500</v>
@@ -1596,16 +1769,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C43" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E43">
         <v>16500</v>
@@ -1613,7 +1786,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B44" t="s">
         <v>25</v>
@@ -1630,16 +1803,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B45" t="s">
+        <v>51</v>
+      </c>
+      <c r="C45" t="s">
         <v>52</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" s="5" t="s">
         <v>53</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>54</v>
       </c>
       <c r="E45">
         <v>400</v>
@@ -1647,16 +1820,16 @@
     </row>
     <row r="46" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="7" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B46" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C46" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="D46" s="8" t="s">
         <v>56</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>57</v>
       </c>
       <c r="E46" s="7">
         <v>400</v>
@@ -1664,16 +1837,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B47" t="s">
+        <v>60</v>
+      </c>
+      <c r="C47" t="s">
         <v>61</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="E47">
         <v>704</v>
@@ -1681,16 +1854,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B48" t="s">
+        <v>63</v>
+      </c>
+      <c r="C48" t="s">
         <v>64</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>66</v>
       </c>
       <c r="E48">
         <v>602</v>
@@ -1698,16 +1871,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B49" t="s">
+        <v>81</v>
+      </c>
+      <c r="C49" t="s">
         <v>82</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>84</v>
       </c>
       <c r="E49">
         <v>128</v>
@@ -1715,16 +1888,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B50" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C50" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E50">
         <v>825</v>
@@ -1738,7 +1911,7 @@
         <v>10</v>
       </c>
       <c r="C51" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D51" s="10"/>
       <c r="E51">
@@ -1747,11 +1920,11 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B52" s="11"/>
       <c r="C52" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D52" s="10"/>
       <c r="E52">
@@ -1771,56 +1944,90 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="D5" r:id="rId1" xr:uid="{80EE9128-EF22-45E1-A050-B4A922D7A5A4}"/>
-    <hyperlink ref="D25" r:id="rId2" xr:uid="{CA6F2ACE-9B39-4D45-9C20-19A5DB6D12CA}"/>
-    <hyperlink ref="D15" r:id="rId3" xr:uid="{892A1EEC-B028-4BF1-ADCD-AF96A0988B50}"/>
-    <hyperlink ref="D10" r:id="rId4" xr:uid="{F1426B06-7CBB-4D59-AE83-B095FA6474E2}"/>
-    <hyperlink ref="D8" r:id="rId5" xr:uid="{592D78FC-336C-471A-91BD-1562E94DA284}"/>
-    <hyperlink ref="D9" r:id="rId6" xr:uid="{A2D386D9-0502-4921-BB61-A819FF837370}"/>
-    <hyperlink ref="D19" r:id="rId7" xr:uid="{7BE3DA68-E823-4B16-885B-945823145A4E}"/>
-    <hyperlink ref="D13" r:id="rId8" xr:uid="{5A89EF2A-F868-480F-9E72-4F25C74088A4}"/>
-    <hyperlink ref="D31" r:id="rId9" xr:uid="{99947C2E-DEFB-4F3D-B10B-4C51E1A36A2A}"/>
-    <hyperlink ref="D33" r:id="rId10" xr:uid="{8D11C5C3-9012-49EE-A7E5-072DFCD7E4CB}"/>
-    <hyperlink ref="D2" r:id="rId11" xr:uid="{6CF4DEC1-CD4E-4844-A06E-A3B5553E4A0A}"/>
-    <hyperlink ref="D3" r:id="rId12" xr:uid="{9E806015-46CC-43F4-B15B-0F80E18DD0D3}"/>
-    <hyperlink ref="D4" r:id="rId13" xr:uid="{0BE1B822-D34C-40EF-8B0F-F98C95A68F23}"/>
-    <hyperlink ref="D11" r:id="rId14" xr:uid="{BD02D7C7-CF92-4415-BD68-A5E1CD860AB5}"/>
-    <hyperlink ref="D16" r:id="rId15" xr:uid="{B21EE433-AA31-44F8-A2B5-B896D27134D4}"/>
-    <hyperlink ref="D14" r:id="rId16" xr:uid="{E2D6E56A-BEDF-4371-A57A-AE46E0B0D271}"/>
-    <hyperlink ref="D17" r:id="rId17" xr:uid="{6EEDF604-934E-4BBF-844F-1CBB5949AF7F}"/>
-    <hyperlink ref="D18" r:id="rId18" xr:uid="{2D6E9249-18AB-4397-B0F5-437EFBC6F332}"/>
-    <hyperlink ref="D36" r:id="rId19" xr:uid="{E63D41F9-5B08-43E0-8053-0724E6D37B6B}"/>
-    <hyperlink ref="D21" r:id="rId20" xr:uid="{5BA1C18C-D565-4734-9906-9C0A7DC7BFEA}"/>
-    <hyperlink ref="D27" r:id="rId21" xr:uid="{40D3F8D6-8B9A-4507-8102-4BFB0D9B2580}"/>
-    <hyperlink ref="D26" r:id="rId22" xr:uid="{EFEDD41E-1E02-461C-9393-AD2ACCBC2A60}"/>
-    <hyperlink ref="D32" r:id="rId23" xr:uid="{0BEBBA09-865C-426C-A4B4-4F2481A2A4E8}"/>
-    <hyperlink ref="D12" r:id="rId24" xr:uid="{9B82FEF9-0E16-4B92-A3E1-1FC2CB2AF171}"/>
-    <hyperlink ref="D7" r:id="rId25" xr:uid="{2ED0409A-8763-4061-A855-6C9AC6A9D6BD}"/>
-    <hyperlink ref="D28" r:id="rId26" xr:uid="{A6B3F117-56EC-4411-89C5-2B81B32C6D2F}"/>
-    <hyperlink ref="D29" r:id="rId27" xr:uid="{45AB639A-6A68-47E6-820F-5AE96EF37CCE}"/>
-    <hyperlink ref="D30" r:id="rId28" xr:uid="{7CB307A7-AD29-447B-B87B-FDF01946BA4A}"/>
-    <hyperlink ref="D24" r:id="rId29" xr:uid="{D83D9F73-94C9-4362-9F33-9764794F83C7}"/>
-    <hyperlink ref="D23" r:id="rId30" xr:uid="{13D49606-5D63-4601-9617-2606341647E2}"/>
-    <hyperlink ref="D34" r:id="rId31" xr:uid="{E93DF50E-6385-47B4-B2C7-B9246E51EFC3}"/>
-    <hyperlink ref="D40" r:id="rId32" xr:uid="{887D03B3-F5B5-4EC3-B378-CFF1ACACC697}"/>
-    <hyperlink ref="D41" r:id="rId33" xr:uid="{25328B39-D4E0-444C-9000-8F992DB7BA09}"/>
-    <hyperlink ref="D20" r:id="rId34" xr:uid="{80ECF8CD-7A79-402A-B5EC-F9BA63C3B50A}"/>
-    <hyperlink ref="D43" r:id="rId35" xr:uid="{6B7E0906-BF85-4BF1-A5E5-9F4F8AB12E12}"/>
-    <hyperlink ref="D42" r:id="rId36" xr:uid="{A757999D-BA12-4BC4-B318-11BE5E932894}"/>
-    <hyperlink ref="D38" r:id="rId37" xr:uid="{6AF44C4C-D5AE-4BD7-8C44-C3D0460467C0}"/>
-    <hyperlink ref="D35" r:id="rId38" xr:uid="{368C86F0-6C72-4FCF-9F6B-86FBA36B83AF}"/>
-    <hyperlink ref="D6" r:id="rId39" xr:uid="{705A06BF-AD9E-4AEF-8BEC-6580A15197D6}"/>
-    <hyperlink ref="D37" r:id="rId40" xr:uid="{6683E2F8-FB9A-4014-9996-7FEAAC683B93}"/>
-    <hyperlink ref="D44" r:id="rId41" xr:uid="{F581F61C-236D-49A3-AE06-C2A7FF968C89}"/>
-    <hyperlink ref="D45" r:id="rId42" xr:uid="{BB91F514-736D-4FC9-A32E-788A20E577B9}"/>
-    <hyperlink ref="D46" r:id="rId43" xr:uid="{7EBDAD46-1A5B-4B2C-AF3D-61F18C3E275F}"/>
-    <hyperlink ref="D47" r:id="rId44" xr:uid="{A36D56AA-7C90-4154-A870-DA9409189D1F}"/>
-    <hyperlink ref="D22" r:id="rId45" xr:uid="{6E85802D-CC4C-4BD4-83ED-55100DE115BA}"/>
-    <hyperlink ref="D48" r:id="rId46" xr:uid="{00DDF648-5623-4E1D-8FC4-42D38FAEE4CA}"/>
-    <hyperlink ref="D49" r:id="rId47" xr:uid="{77EAAAD6-086C-4DCF-9B24-E59430A2E2FB}"/>
-    <hyperlink ref="D50" r:id="rId48" xr:uid="{CE8A3876-BF7A-4C23-95FB-161481F8F980}"/>
-    <hyperlink ref="F26" r:id="rId49" xr:uid="{E4CD215B-218A-44EC-9945-5F6AD197B3B2}"/>
-    <hyperlink ref="G26" r:id="rId50" xr:uid="{522CE0D5-7681-455E-9A32-6774CD570260}"/>
-    <hyperlink ref="H26" r:id="rId51" xr:uid="{A440C7F8-BC12-4ED8-80D1-5687F587FDDF}"/>
+    <hyperlink ref="D15" r:id="rId2" xr:uid="{892A1EEC-B028-4BF1-ADCD-AF96A0988B50}"/>
+    <hyperlink ref="D10" r:id="rId3" xr:uid="{F1426B06-7CBB-4D59-AE83-B095FA6474E2}"/>
+    <hyperlink ref="D8" r:id="rId4" xr:uid="{592D78FC-336C-471A-91BD-1562E94DA284}"/>
+    <hyperlink ref="D9" r:id="rId5" xr:uid="{A2D386D9-0502-4921-BB61-A819FF837370}"/>
+    <hyperlink ref="D13" r:id="rId6" xr:uid="{5A89EF2A-F868-480F-9E72-4F25C74088A4}"/>
+    <hyperlink ref="D2" r:id="rId7" xr:uid="{6CF4DEC1-CD4E-4844-A06E-A3B5553E4A0A}"/>
+    <hyperlink ref="D3" r:id="rId8" xr:uid="{9E806015-46CC-43F4-B15B-0F80E18DD0D3}"/>
+    <hyperlink ref="D4" r:id="rId9" xr:uid="{0BE1B822-D34C-40EF-8B0F-F98C95A68F23}"/>
+    <hyperlink ref="D11" r:id="rId10" xr:uid="{BD02D7C7-CF92-4415-BD68-A5E1CD860AB5}"/>
+    <hyperlink ref="D14" r:id="rId11" xr:uid="{E2D6E56A-BEDF-4371-A57A-AE46E0B0D271}"/>
+    <hyperlink ref="D12" r:id="rId12" xr:uid="{9B82FEF9-0E16-4B92-A3E1-1FC2CB2AF171}"/>
+    <hyperlink ref="D7" r:id="rId13" xr:uid="{2ED0409A-8763-4061-A855-6C9AC6A9D6BD}"/>
+    <hyperlink ref="D40" r:id="rId14" xr:uid="{887D03B3-F5B5-4EC3-B378-CFF1ACACC697}"/>
+    <hyperlink ref="D41" r:id="rId15" xr:uid="{25328B39-D4E0-444C-9000-8F992DB7BA09}"/>
+    <hyperlink ref="D43" r:id="rId16" xr:uid="{6B7E0906-BF85-4BF1-A5E5-9F4F8AB12E12}"/>
+    <hyperlink ref="D42" r:id="rId17" xr:uid="{A757999D-BA12-4BC4-B318-11BE5E932894}"/>
+    <hyperlink ref="D6" r:id="rId18" xr:uid="{705A06BF-AD9E-4AEF-8BEC-6580A15197D6}"/>
+    <hyperlink ref="D44" r:id="rId19" xr:uid="{F581F61C-236D-49A3-AE06-C2A7FF968C89}"/>
+    <hyperlink ref="D45" r:id="rId20" xr:uid="{BB91F514-736D-4FC9-A32E-788A20E577B9}"/>
+    <hyperlink ref="D46" r:id="rId21" xr:uid="{7EBDAD46-1A5B-4B2C-AF3D-61F18C3E275F}"/>
+    <hyperlink ref="D47" r:id="rId22" xr:uid="{A36D56AA-7C90-4154-A870-DA9409189D1F}"/>
+    <hyperlink ref="D48" r:id="rId23" xr:uid="{00DDF648-5623-4E1D-8FC4-42D38FAEE4CA}"/>
+    <hyperlink ref="D49" r:id="rId24" xr:uid="{77EAAAD6-086C-4DCF-9B24-E59430A2E2FB}"/>
+    <hyperlink ref="D50" r:id="rId25" xr:uid="{CE8A3876-BF7A-4C23-95FB-161481F8F980}"/>
+    <hyperlink ref="F26" r:id="rId26" xr:uid="{E4CD215B-218A-44EC-9945-5F6AD197B3B2}"/>
+    <hyperlink ref="G26" r:id="rId27" xr:uid="{522CE0D5-7681-455E-9A32-6774CD570260}"/>
+    <hyperlink ref="H26" r:id="rId28" xr:uid="{A440C7F8-BC12-4ED8-80D1-5687F587FDDF}"/>
+    <hyperlink ref="G2" r:id="rId29" xr:uid="{E92EE150-871A-439E-974B-FA2049C8CA38}"/>
+    <hyperlink ref="H2" r:id="rId30" xr:uid="{03D46786-9004-478B-A395-4AA7EF082A56}"/>
+    <hyperlink ref="I2" r:id="rId31" xr:uid="{57A7AAAC-E898-44F4-A3B0-AF97E1EBFE69}"/>
+    <hyperlink ref="J2" r:id="rId32" xr:uid="{ACBBE8A2-CC26-4054-A6DA-6E5C07960AD1}"/>
+    <hyperlink ref="F3" r:id="rId33" xr:uid="{29114336-215A-43FA-8297-CDDD761C1501}"/>
+    <hyperlink ref="G3" r:id="rId34" xr:uid="{0AE835A0-8DDB-4A91-8176-2AFF9C2AEA07}"/>
+    <hyperlink ref="F4" r:id="rId35" xr:uid="{9F1D3B58-9986-4688-ABF5-8FF2375FBF82}"/>
+    <hyperlink ref="G4" r:id="rId36" xr:uid="{6CB43155-6638-4798-B491-DB6FA525EB50}"/>
+    <hyperlink ref="F5" r:id="rId37" xr:uid="{7DCFF457-0664-4586-B064-437E516400A0}"/>
+    <hyperlink ref="G5" r:id="rId38" xr:uid="{343CFCD0-DE46-476D-8E81-253A8E3B316C}"/>
+    <hyperlink ref="F6" r:id="rId39" xr:uid="{3EC21E9D-842C-4CB8-B811-D23F2C778BF7}"/>
+    <hyperlink ref="G6" r:id="rId40" xr:uid="{33FCB128-9197-43CE-8CB7-FE8F3059BE4F}"/>
+    <hyperlink ref="H6" r:id="rId41" xr:uid="{1F8966A1-2290-4CEF-BB02-FC990CD8D791}"/>
+    <hyperlink ref="F7" r:id="rId42" xr:uid="{423CFF82-45DF-4D68-BB50-979F20779C0F}"/>
+    <hyperlink ref="F8" r:id="rId43" xr:uid="{E5CBA92A-AB4F-478A-9CFE-9419577F0ED5}"/>
+    <hyperlink ref="F10" r:id="rId44" xr:uid="{EB116F53-35BE-4168-A3B3-A6B7F3013480}"/>
+    <hyperlink ref="F9" r:id="rId45" xr:uid="{AAFC07D3-B9CC-483D-8F88-4D08FD7ED6B1}"/>
+    <hyperlink ref="F11" r:id="rId46" xr:uid="{E9FA1CD4-77B0-4337-B7D9-41FF5FAF8D5C}"/>
+    <hyperlink ref="G11" r:id="rId47" xr:uid="{44406BDF-4864-4DEE-8D3F-960771AC5EEA}"/>
+    <hyperlink ref="F12" r:id="rId48" xr:uid="{A2470070-51EF-4670-833B-8D482C601671}"/>
+    <hyperlink ref="F13" r:id="rId49" xr:uid="{4D4972B4-0A24-4319-992B-3F7B5C4CCDCE}"/>
+    <hyperlink ref="F14" r:id="rId50" xr:uid="{AE1ACB1F-F85D-4CF3-AC72-FD2F25C8E4B2}"/>
+    <hyperlink ref="D22" r:id="rId51" xr:uid="{6E85802D-CC4C-4BD4-83ED-55100DE115BA}"/>
+    <hyperlink ref="D37" r:id="rId52" xr:uid="{6683E2F8-FB9A-4014-9996-7FEAAC683B93}"/>
+    <hyperlink ref="D35" r:id="rId53" xr:uid="{368C86F0-6C72-4FCF-9F6B-86FBA36B83AF}"/>
+    <hyperlink ref="D38" r:id="rId54" xr:uid="{6AF44C4C-D5AE-4BD7-8C44-C3D0460467C0}"/>
+    <hyperlink ref="D20" r:id="rId55" xr:uid="{80ECF8CD-7A79-402A-B5EC-F9BA63C3B50A}"/>
+    <hyperlink ref="D34" r:id="rId56" xr:uid="{E93DF50E-6385-47B4-B2C7-B9246E51EFC3}"/>
+    <hyperlink ref="D23" r:id="rId57" xr:uid="{13D49606-5D63-4601-9617-2606341647E2}"/>
+    <hyperlink ref="D24" r:id="rId58" xr:uid="{D83D9F73-94C9-4362-9F33-9764794F83C7}"/>
+    <hyperlink ref="D30" r:id="rId59" xr:uid="{7CB307A7-AD29-447B-B87B-FDF01946BA4A}"/>
+    <hyperlink ref="D29" r:id="rId60" xr:uid="{45AB639A-6A68-47E6-820F-5AE96EF37CCE}"/>
+    <hyperlink ref="D28" r:id="rId61" xr:uid="{A6B3F117-56EC-4411-89C5-2B81B32C6D2F}"/>
+    <hyperlink ref="D32" r:id="rId62" xr:uid="{0BEBBA09-865C-426C-A4B4-4F2481A2A4E8}"/>
+    <hyperlink ref="D26" r:id="rId63" xr:uid="{EFEDD41E-1E02-461C-9393-AD2ACCBC2A60}"/>
+    <hyperlink ref="D27" r:id="rId64" xr:uid="{40D3F8D6-8B9A-4507-8102-4BFB0D9B2580}"/>
+    <hyperlink ref="D21" r:id="rId65" xr:uid="{5BA1C18C-D565-4734-9906-9C0A7DC7BFEA}"/>
+    <hyperlink ref="D36" r:id="rId66" xr:uid="{E63D41F9-5B08-43E0-8053-0724E6D37B6B}"/>
+    <hyperlink ref="D18" r:id="rId67" xr:uid="{2D6E9249-18AB-4397-B0F5-437EFBC6F332}"/>
+    <hyperlink ref="D17" r:id="rId68" xr:uid="{6EEDF604-934E-4BBF-844F-1CBB5949AF7F}"/>
+    <hyperlink ref="D16" r:id="rId69" xr:uid="{B21EE433-AA31-44F8-A2B5-B896D27134D4}"/>
+    <hyperlink ref="D33" r:id="rId70" xr:uid="{8D11C5C3-9012-49EE-A7E5-072DFCD7E4CB}"/>
+    <hyperlink ref="D31" r:id="rId71" xr:uid="{99947C2E-DEFB-4F3D-B10B-4C51E1A36A2A}"/>
+    <hyperlink ref="D19" r:id="rId72" xr:uid="{7BE3DA68-E823-4B16-885B-945823145A4E}"/>
+    <hyperlink ref="D25" r:id="rId73" xr:uid="{CA6F2ACE-9B39-4D45-9C20-19A5DB6D12CA}"/>
+    <hyperlink ref="F15" r:id="rId74" xr:uid="{C35D8A0A-F10A-40F3-A7C3-C5AA6BBB28B5}"/>
+    <hyperlink ref="F16" r:id="rId75" xr:uid="{AEA8472C-440C-4C92-8A77-FEF9C839BF0D}"/>
+    <hyperlink ref="G16" r:id="rId76" xr:uid="{D288EC2B-5C10-4124-87EF-58A40C745452}"/>
+    <hyperlink ref="H16" r:id="rId77" xr:uid="{AB6F38F4-9CD4-49B8-9315-6A116F3871B3}"/>
+    <hyperlink ref="G17" r:id="rId78" xr:uid="{A5B70704-22DA-478D-9DD9-DCC7AA836C2E}"/>
+    <hyperlink ref="F17" r:id="rId79" xr:uid="{5D05AAA5-6C4E-4951-8A01-ED8966A74C6F}"/>
+    <hyperlink ref="H17" r:id="rId80" xr:uid="{F455D43D-0AE8-4F39-B8B8-A9E496C9515D}"/>
+    <hyperlink ref="F18" r:id="rId81" xr:uid="{5119747E-83D1-43AE-B78D-77BFA9310B65}"/>
+    <hyperlink ref="G18" r:id="rId82" xr:uid="{79EB751C-298E-437E-BEE6-FA6698B99FB9}"/>
+    <hyperlink ref="H18" r:id="rId83" xr:uid="{0509DA5B-CB9D-43F8-8168-2BABDCB86042}"/>
+    <hyperlink ref="I18" r:id="rId84" xr:uid="{ECC362EA-7284-4D5F-961E-DDABCD606149}"/>
+    <hyperlink ref="J18" r:id="rId85" xr:uid="{C4D0C97C-3218-467C-949C-4AE1EBBC383C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Locations.xlsx
+++ b/data/Locations.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\landscapingUOB-api\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98D4AEE-B9BD-48DF-9BC7-7CE0E90A0793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB9B7452-C7BB-4755-84F4-39E4B7FBFD27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="160">
   <si>
     <t>Location type</t>
   </si>
@@ -191,24 +191,9 @@
     <t>https://i.postimg.cc/bvBKCNZ0/S38-1.jpg</t>
   </si>
   <si>
-    <t>S39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">College of Law </t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/26jVwGBL/S39.jpg</t>
   </si>
   <si>
-    <t>S39A</t>
-  </si>
-  <si>
-    <t>Legal Clinic Office</t>
-  </si>
-  <si>
-    <t>https://i.postimg.cc/y8mhfRd7/S39A.jpg</t>
-  </si>
-  <si>
     <t>S4</t>
   </si>
   <si>
@@ -341,18 +326,6 @@
     <t>https://i.postimg.cc/wx1GwWdH/S54-2.jpg</t>
   </si>
   <si>
-    <t>S56</t>
-  </si>
-  <si>
-    <t>Trade Workshop</t>
-  </si>
-  <si>
-    <t>https://i.postimg.cc/mrYRjcZ6/S56-2.jpg</t>
-  </si>
-  <si>
-    <t>S57</t>
-  </si>
-  <si>
     <t>Business Incubator Center</t>
   </si>
   <si>
@@ -368,12 +341,6 @@
     <t>Infrastructure</t>
   </si>
   <si>
-    <t>S1</t>
-  </si>
-  <si>
-    <t>Boundary Wall</t>
-  </si>
-  <si>
     <t>Facilities</t>
   </si>
   <si>
@@ -522,6 +489,33 @@
   </si>
   <si>
     <t>https://i.postimg.cc/wxC15vc6/S39-3.jpg</t>
+  </si>
+  <si>
+    <t>S56, S57</t>
+  </si>
+  <si>
+    <t>S39, S39A</t>
+  </si>
+  <si>
+    <t>College of Law, Legal Clinic Office</t>
+  </si>
+  <si>
+    <t>Boundary Wall - Main Gate</t>
+  </si>
+  <si>
+    <t>Boundary Wall - Western Gate</t>
+  </si>
+  <si>
+    <t>Boundary Wall - Eastern Gate</t>
+  </si>
+  <si>
+    <t>Gate 1</t>
+  </si>
+  <si>
+    <t>Gate 2</t>
+  </si>
+  <si>
+    <t>Gate 3</t>
   </si>
 </sst>
 </file>
@@ -557,18 +551,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -578,13 +566,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFE163"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -620,19 +602,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -914,7 +898,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.90625" customWidth="1"/>
@@ -934,7 +918,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
@@ -943,22 +927,22 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -977,20 +961,20 @@
       <c r="E2">
         <v>699</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="I2" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="J2" s="13" t="s">
-        <v>144</v>
+      <c r="G2" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -1009,11 +993,11 @@
       <c r="E3">
         <v>600</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="13" t="s">
-        <v>145</v>
+      <c r="G3" s="8" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
@@ -1032,11 +1016,11 @@
       <c r="E4">
         <v>350</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="13" t="s">
-        <v>146</v>
+      <c r="G4" s="8" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
@@ -1055,11 +1039,11 @@
       <c r="E5">
         <v>186</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="13" t="s">
-        <v>147</v>
+      <c r="G5" s="8" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -1078,14 +1062,14 @@
       <c r="E6">
         <v>77</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>149</v>
+      <c r="G6" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
@@ -1104,7 +1088,7 @@
       <c r="E7">
         <v>330</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="8" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1124,7 +1108,7 @@
       <c r="E8">
         <v>280</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="8" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1144,7 +1128,7 @@
       <c r="E9">
         <v>270</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1164,7 +1148,7 @@
       <c r="E10">
         <v>120</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="8" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1184,11 +1168,11 @@
       <c r="E11">
         <v>440</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="G11" s="13" t="s">
-        <v>152</v>
+      <c r="G11" s="8" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
@@ -1207,7 +1191,7 @@
       <c r="E12">
         <v>105</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="8" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1227,7 +1211,7 @@
       <c r="E13">
         <v>1050</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="8" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1247,7 +1231,7 @@
       <c r="E14">
         <v>80</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F14" s="8" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1267,7 +1251,7 @@
       <c r="E15">
         <v>145</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="8" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1282,19 +1266,19 @@
         <v>47</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E16">
         <v>1350</v>
       </c>
-      <c r="F16" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>155</v>
+      <c r="F16" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
@@ -1313,14 +1297,14 @@
       <c r="E17">
         <v>175</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="F17" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="G17" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>157</v>
+      <c r="G17" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
@@ -1328,48 +1312,48 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
+        <v>152</v>
+      </c>
+      <c r="C18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="C18" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>53</v>
       </c>
       <c r="E18">
         <v>1000</v>
       </c>
-      <c r="F18" s="13" t="s">
+      <c r="F18" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" t="s">
         <v>53</v>
       </c>
-      <c r="G18" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="J18" s="13" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B19" s="7" t="s">
+      <c r="D19" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19" s="7">
-        <v>1000</v>
+      <c r="E19">
+        <v>350</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
@@ -1377,16 +1361,16 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C20" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>59</v>
-      </c>
       <c r="E20">
-        <v>350</v>
+        <v>464</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
@@ -1394,16 +1378,16 @@
         <v>3</v>
       </c>
       <c r="B21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C21" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>62</v>
-      </c>
       <c r="E21">
-        <v>464</v>
+        <v>310</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
@@ -1411,16 +1395,16 @@
         <v>3</v>
       </c>
       <c r="B22" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" t="s">
+        <v>62</v>
+      </c>
+      <c r="D22" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C22" t="s">
-        <v>64</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>65</v>
-      </c>
       <c r="E22">
-        <v>310</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
@@ -1428,16 +1412,16 @@
         <v>3</v>
       </c>
       <c r="B23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C23" t="s">
-        <v>67</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>68</v>
-      </c>
       <c r="E23">
-        <v>195</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
@@ -1445,16 +1429,16 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>71</v>
-      </c>
       <c r="E24">
-        <v>45</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
@@ -1462,73 +1446,73 @@
         <v>3</v>
       </c>
       <c r="B25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C25" t="s">
+      <c r="E25">
+        <v>90</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" t="s">
         <v>73</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="C26" t="s">
         <v>74</v>
       </c>
-      <c r="E25">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>3</v>
-      </c>
-      <c r="B26" t="s">
+      <c r="D26" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C26" t="s">
+      <c r="E26">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="C27" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="E26">
-        <v>90</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="G26" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="H26" s="13" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>3</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="D27" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C27" t="s">
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" t="s">
         <v>79</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="C28" t="s">
         <v>80</v>
       </c>
-      <c r="E27">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B28" s="7" t="s">
+      <c r="D28" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>83</v>
+      <c r="E28">
+        <v>399</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
@@ -1536,16 +1520,16 @@
         <v>3</v>
       </c>
       <c r="B29" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" t="s">
+        <v>83</v>
+      </c>
+      <c r="D29" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C29" t="s">
-        <v>85</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>86</v>
-      </c>
       <c r="E29">
-        <v>399</v>
+        <v>163</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
@@ -1553,16 +1537,16 @@
         <v>3</v>
       </c>
       <c r="B30" t="s">
+        <v>85</v>
+      </c>
+      <c r="C30" t="s">
+        <v>86</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C30" t="s">
-        <v>88</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>89</v>
-      </c>
       <c r="E30">
-        <v>163</v>
+        <v>194</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
@@ -1570,16 +1554,16 @@
         <v>3</v>
       </c>
       <c r="B31" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D31" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C31" t="s">
-        <v>91</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>92</v>
-      </c>
       <c r="E31">
-        <v>194</v>
+        <v>373</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
@@ -1587,164 +1571,154 @@
         <v>3</v>
       </c>
       <c r="B32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C32" t="s">
+        <v>83</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E32">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C33" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D33" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E32">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>3</v>
-      </c>
-      <c r="B33" t="s">
+      <c r="E33" s="6">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C34" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="C33" t="s">
-        <v>88</v>
-      </c>
-      <c r="D33" s="5" t="s">
+      <c r="D34" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="E33">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B34" s="7" t="s">
+      <c r="E34" s="9">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>3</v>
+      </c>
+      <c r="B35" t="s">
         <v>98</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C35" t="s">
         <v>99</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D35" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="E35">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E34" s="7">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="E35" s="7">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="E36" s="7">
-        <v>205</v>
+      <c r="B36" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="C36" t="s">
+        <v>154</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="E36">
+        <v>142</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>3</v>
+      <c r="A37" s="3" t="s">
+        <v>100</v>
       </c>
       <c r="B37" t="s">
-        <v>107</v>
+        <v>158</v>
       </c>
       <c r="C37" t="s">
-        <v>108</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="E37">
-        <v>350</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="D37" s="12"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>110</v>
+        <v>100</v>
+      </c>
+      <c r="B38" t="s">
+        <v>159</v>
       </c>
       <c r="C38" t="s">
-        <v>111</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="E38">
-        <v>142</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="D38" s="12"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B39" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C39" t="s">
-        <v>128</v>
-      </c>
-      <c r="D39" s="9"/>
+        <v>117</v>
+      </c>
+      <c r="D39" s="12"/>
       <c r="E39">
         <v>1300</v>
       </c>
     </row>
-    <row r="40" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="E40" s="7">
+    <row r="40" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E40" s="6">
         <v>600</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="B41" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="E41">
         <v>5300</v>
@@ -1752,16 +1726,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="B42" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="C42" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E42">
         <v>16500</v>
@@ -1769,16 +1743,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="B43" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="C43" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="E43">
         <v>16500</v>
@@ -1786,7 +1760,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B44" t="s">
         <v>25</v>
@@ -1803,131 +1777,114 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B45" t="s">
+        <v>152</v>
+      </c>
+      <c r="C45" t="s">
+        <v>153</v>
+      </c>
+      <c r="D45" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="C45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>53</v>
       </c>
       <c r="E45">
         <v>400</v>
       </c>
     </row>
-    <row r="46" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C46" s="7" t="s">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>116</v>
+      </c>
+      <c r="B46" t="s">
         <v>55</v>
       </c>
-      <c r="D46" s="8" t="s">
+      <c r="C46" t="s">
         <v>56</v>
       </c>
-      <c r="E46" s="7">
-        <v>400</v>
+      <c r="D46" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E46">
+        <v>704</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B47" t="s">
+        <v>58</v>
+      </c>
+      <c r="C47" t="s">
+        <v>59</v>
+      </c>
+      <c r="D47" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C47" t="s">
-        <v>61</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>62</v>
-      </c>
       <c r="E47">
-        <v>704</v>
+        <v>602</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B48" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C48" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="E48">
-        <v>602</v>
+        <v>128</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B49" t="s">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="C49" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="E49">
-        <v>128</v>
+        <v>825</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>127</v>
-      </c>
-      <c r="B50" t="s">
-        <v>123</v>
+        <v>3</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>10</v>
       </c>
       <c r="C50" t="s">
-        <v>124</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>125</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="D50" s="10"/>
       <c r="E50">
-        <v>825</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>3</v>
-      </c>
-      <c r="B51" s="12" t="s">
-        <v>10</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="B51" s="11"/>
       <c r="C51" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="D51" s="10"/>
       <c r="E51">
-        <v>2550</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>130</v>
-      </c>
-      <c r="B52" s="11"/>
-      <c r="C52" t="s">
-        <v>131</v>
-      </c>
-      <c r="D52" s="10"/>
-      <c r="E52">
         <v>13500</v>
       </c>
     </row>
@@ -1963,71 +1920,68 @@
     <hyperlink ref="D6" r:id="rId18" xr:uid="{705A06BF-AD9E-4AEF-8BEC-6580A15197D6}"/>
     <hyperlink ref="D44" r:id="rId19" xr:uid="{F581F61C-236D-49A3-AE06-C2A7FF968C89}"/>
     <hyperlink ref="D45" r:id="rId20" xr:uid="{BB91F514-736D-4FC9-A32E-788A20E577B9}"/>
-    <hyperlink ref="D46" r:id="rId21" xr:uid="{7EBDAD46-1A5B-4B2C-AF3D-61F18C3E275F}"/>
-    <hyperlink ref="D47" r:id="rId22" xr:uid="{A36D56AA-7C90-4154-A870-DA9409189D1F}"/>
-    <hyperlink ref="D48" r:id="rId23" xr:uid="{00DDF648-5623-4E1D-8FC4-42D38FAEE4CA}"/>
-    <hyperlink ref="D49" r:id="rId24" xr:uid="{77EAAAD6-086C-4DCF-9B24-E59430A2E2FB}"/>
-    <hyperlink ref="D50" r:id="rId25" xr:uid="{CE8A3876-BF7A-4C23-95FB-161481F8F980}"/>
-    <hyperlink ref="F26" r:id="rId26" xr:uid="{E4CD215B-218A-44EC-9945-5F6AD197B3B2}"/>
-    <hyperlink ref="G26" r:id="rId27" xr:uid="{522CE0D5-7681-455E-9A32-6774CD570260}"/>
-    <hyperlink ref="H26" r:id="rId28" xr:uid="{A440C7F8-BC12-4ED8-80D1-5687F587FDDF}"/>
-    <hyperlink ref="G2" r:id="rId29" xr:uid="{E92EE150-871A-439E-974B-FA2049C8CA38}"/>
-    <hyperlink ref="H2" r:id="rId30" xr:uid="{03D46786-9004-478B-A395-4AA7EF082A56}"/>
-    <hyperlink ref="I2" r:id="rId31" xr:uid="{57A7AAAC-E898-44F4-A3B0-AF97E1EBFE69}"/>
-    <hyperlink ref="J2" r:id="rId32" xr:uid="{ACBBE8A2-CC26-4054-A6DA-6E5C07960AD1}"/>
-    <hyperlink ref="F3" r:id="rId33" xr:uid="{29114336-215A-43FA-8297-CDDD761C1501}"/>
-    <hyperlink ref="G3" r:id="rId34" xr:uid="{0AE835A0-8DDB-4A91-8176-2AFF9C2AEA07}"/>
-    <hyperlink ref="F4" r:id="rId35" xr:uid="{9F1D3B58-9986-4688-ABF5-8FF2375FBF82}"/>
-    <hyperlink ref="G4" r:id="rId36" xr:uid="{6CB43155-6638-4798-B491-DB6FA525EB50}"/>
-    <hyperlink ref="F5" r:id="rId37" xr:uid="{7DCFF457-0664-4586-B064-437E516400A0}"/>
-    <hyperlink ref="G5" r:id="rId38" xr:uid="{343CFCD0-DE46-476D-8E81-253A8E3B316C}"/>
-    <hyperlink ref="F6" r:id="rId39" xr:uid="{3EC21E9D-842C-4CB8-B811-D23F2C778BF7}"/>
-    <hyperlink ref="G6" r:id="rId40" xr:uid="{33FCB128-9197-43CE-8CB7-FE8F3059BE4F}"/>
-    <hyperlink ref="H6" r:id="rId41" xr:uid="{1F8966A1-2290-4CEF-BB02-FC990CD8D791}"/>
-    <hyperlink ref="F7" r:id="rId42" xr:uid="{423CFF82-45DF-4D68-BB50-979F20779C0F}"/>
-    <hyperlink ref="F8" r:id="rId43" xr:uid="{E5CBA92A-AB4F-478A-9CFE-9419577F0ED5}"/>
-    <hyperlink ref="F10" r:id="rId44" xr:uid="{EB116F53-35BE-4168-A3B3-A6B7F3013480}"/>
-    <hyperlink ref="F9" r:id="rId45" xr:uid="{AAFC07D3-B9CC-483D-8F88-4D08FD7ED6B1}"/>
-    <hyperlink ref="F11" r:id="rId46" xr:uid="{E9FA1CD4-77B0-4337-B7D9-41FF5FAF8D5C}"/>
-    <hyperlink ref="G11" r:id="rId47" xr:uid="{44406BDF-4864-4DEE-8D3F-960771AC5EEA}"/>
-    <hyperlink ref="F12" r:id="rId48" xr:uid="{A2470070-51EF-4670-833B-8D482C601671}"/>
-    <hyperlink ref="F13" r:id="rId49" xr:uid="{4D4972B4-0A24-4319-992B-3F7B5C4CCDCE}"/>
-    <hyperlink ref="F14" r:id="rId50" xr:uid="{AE1ACB1F-F85D-4CF3-AC72-FD2F25C8E4B2}"/>
-    <hyperlink ref="D22" r:id="rId51" xr:uid="{6E85802D-CC4C-4BD4-83ED-55100DE115BA}"/>
-    <hyperlink ref="D37" r:id="rId52" xr:uid="{6683E2F8-FB9A-4014-9996-7FEAAC683B93}"/>
-    <hyperlink ref="D35" r:id="rId53" xr:uid="{368C86F0-6C72-4FCF-9F6B-86FBA36B83AF}"/>
-    <hyperlink ref="D38" r:id="rId54" xr:uid="{6AF44C4C-D5AE-4BD7-8C44-C3D0460467C0}"/>
-    <hyperlink ref="D20" r:id="rId55" xr:uid="{80ECF8CD-7A79-402A-B5EC-F9BA63C3B50A}"/>
-    <hyperlink ref="D34" r:id="rId56" xr:uid="{E93DF50E-6385-47B4-B2C7-B9246E51EFC3}"/>
-    <hyperlink ref="D23" r:id="rId57" xr:uid="{13D49606-5D63-4601-9617-2606341647E2}"/>
-    <hyperlink ref="D24" r:id="rId58" xr:uid="{D83D9F73-94C9-4362-9F33-9764794F83C7}"/>
-    <hyperlink ref="D30" r:id="rId59" xr:uid="{7CB307A7-AD29-447B-B87B-FDF01946BA4A}"/>
-    <hyperlink ref="D29" r:id="rId60" xr:uid="{45AB639A-6A68-47E6-820F-5AE96EF37CCE}"/>
-    <hyperlink ref="D28" r:id="rId61" xr:uid="{A6B3F117-56EC-4411-89C5-2B81B32C6D2F}"/>
-    <hyperlink ref="D32" r:id="rId62" xr:uid="{0BEBBA09-865C-426C-A4B4-4F2481A2A4E8}"/>
-    <hyperlink ref="D26" r:id="rId63" xr:uid="{EFEDD41E-1E02-461C-9393-AD2ACCBC2A60}"/>
-    <hyperlink ref="D27" r:id="rId64" xr:uid="{40D3F8D6-8B9A-4507-8102-4BFB0D9B2580}"/>
-    <hyperlink ref="D21" r:id="rId65" xr:uid="{5BA1C18C-D565-4734-9906-9C0A7DC7BFEA}"/>
-    <hyperlink ref="D36" r:id="rId66" xr:uid="{E63D41F9-5B08-43E0-8053-0724E6D37B6B}"/>
-    <hyperlink ref="D18" r:id="rId67" xr:uid="{2D6E9249-18AB-4397-B0F5-437EFBC6F332}"/>
-    <hyperlink ref="D17" r:id="rId68" xr:uid="{6EEDF604-934E-4BBF-844F-1CBB5949AF7F}"/>
-    <hyperlink ref="D16" r:id="rId69" xr:uid="{B21EE433-AA31-44F8-A2B5-B896D27134D4}"/>
-    <hyperlink ref="D33" r:id="rId70" xr:uid="{8D11C5C3-9012-49EE-A7E5-072DFCD7E4CB}"/>
-    <hyperlink ref="D31" r:id="rId71" xr:uid="{99947C2E-DEFB-4F3D-B10B-4C51E1A36A2A}"/>
-    <hyperlink ref="D19" r:id="rId72" xr:uid="{7BE3DA68-E823-4B16-885B-945823145A4E}"/>
-    <hyperlink ref="D25" r:id="rId73" xr:uid="{CA6F2ACE-9B39-4D45-9C20-19A5DB6D12CA}"/>
-    <hyperlink ref="F15" r:id="rId74" xr:uid="{C35D8A0A-F10A-40F3-A7C3-C5AA6BBB28B5}"/>
-    <hyperlink ref="F16" r:id="rId75" xr:uid="{AEA8472C-440C-4C92-8A77-FEF9C839BF0D}"/>
-    <hyperlink ref="G16" r:id="rId76" xr:uid="{D288EC2B-5C10-4124-87EF-58A40C745452}"/>
-    <hyperlink ref="H16" r:id="rId77" xr:uid="{AB6F38F4-9CD4-49B8-9315-6A116F3871B3}"/>
-    <hyperlink ref="G17" r:id="rId78" xr:uid="{A5B70704-22DA-478D-9DD9-DCC7AA836C2E}"/>
-    <hyperlink ref="F17" r:id="rId79" xr:uid="{5D05AAA5-6C4E-4951-8A01-ED8966A74C6F}"/>
-    <hyperlink ref="H17" r:id="rId80" xr:uid="{F455D43D-0AE8-4F39-B8B8-A9E496C9515D}"/>
-    <hyperlink ref="F18" r:id="rId81" xr:uid="{5119747E-83D1-43AE-B78D-77BFA9310B65}"/>
-    <hyperlink ref="G18" r:id="rId82" xr:uid="{79EB751C-298E-437E-BEE6-FA6698B99FB9}"/>
-    <hyperlink ref="H18" r:id="rId83" xr:uid="{0509DA5B-CB9D-43F8-8168-2BABDCB86042}"/>
-    <hyperlink ref="I18" r:id="rId84" xr:uid="{ECC362EA-7284-4D5F-961E-DDABCD606149}"/>
-    <hyperlink ref="J18" r:id="rId85" xr:uid="{C4D0C97C-3218-467C-949C-4AE1EBBC383C}"/>
+    <hyperlink ref="D46" r:id="rId21" xr:uid="{A36D56AA-7C90-4154-A870-DA9409189D1F}"/>
+    <hyperlink ref="D47" r:id="rId22" xr:uid="{00DDF648-5623-4E1D-8FC4-42D38FAEE4CA}"/>
+    <hyperlink ref="D48" r:id="rId23" xr:uid="{77EAAAD6-086C-4DCF-9B24-E59430A2E2FB}"/>
+    <hyperlink ref="D49" r:id="rId24" xr:uid="{CE8A3876-BF7A-4C23-95FB-161481F8F980}"/>
+    <hyperlink ref="F25" r:id="rId25" xr:uid="{E4CD215B-218A-44EC-9945-5F6AD197B3B2}"/>
+    <hyperlink ref="G25" r:id="rId26" xr:uid="{522CE0D5-7681-455E-9A32-6774CD570260}"/>
+    <hyperlink ref="H25" r:id="rId27" xr:uid="{A440C7F8-BC12-4ED8-80D1-5687F587FDDF}"/>
+    <hyperlink ref="G2" r:id="rId28" xr:uid="{E92EE150-871A-439E-974B-FA2049C8CA38}"/>
+    <hyperlink ref="H2" r:id="rId29" xr:uid="{03D46786-9004-478B-A395-4AA7EF082A56}"/>
+    <hyperlink ref="I2" r:id="rId30" xr:uid="{57A7AAAC-E898-44F4-A3B0-AF97E1EBFE69}"/>
+    <hyperlink ref="J2" r:id="rId31" xr:uid="{ACBBE8A2-CC26-4054-A6DA-6E5C07960AD1}"/>
+    <hyperlink ref="F3" r:id="rId32" xr:uid="{29114336-215A-43FA-8297-CDDD761C1501}"/>
+    <hyperlink ref="G3" r:id="rId33" xr:uid="{0AE835A0-8DDB-4A91-8176-2AFF9C2AEA07}"/>
+    <hyperlink ref="F4" r:id="rId34" xr:uid="{9F1D3B58-9986-4688-ABF5-8FF2375FBF82}"/>
+    <hyperlink ref="G4" r:id="rId35" xr:uid="{6CB43155-6638-4798-B491-DB6FA525EB50}"/>
+    <hyperlink ref="F5" r:id="rId36" xr:uid="{7DCFF457-0664-4586-B064-437E516400A0}"/>
+    <hyperlink ref="G5" r:id="rId37" xr:uid="{343CFCD0-DE46-476D-8E81-253A8E3B316C}"/>
+    <hyperlink ref="F6" r:id="rId38" xr:uid="{3EC21E9D-842C-4CB8-B811-D23F2C778BF7}"/>
+    <hyperlink ref="G6" r:id="rId39" xr:uid="{33FCB128-9197-43CE-8CB7-FE8F3059BE4F}"/>
+    <hyperlink ref="H6" r:id="rId40" xr:uid="{1F8966A1-2290-4CEF-BB02-FC990CD8D791}"/>
+    <hyperlink ref="F7" r:id="rId41" xr:uid="{423CFF82-45DF-4D68-BB50-979F20779C0F}"/>
+    <hyperlink ref="F8" r:id="rId42" xr:uid="{E5CBA92A-AB4F-478A-9CFE-9419577F0ED5}"/>
+    <hyperlink ref="F10" r:id="rId43" xr:uid="{EB116F53-35BE-4168-A3B3-A6B7F3013480}"/>
+    <hyperlink ref="F9" r:id="rId44" xr:uid="{AAFC07D3-B9CC-483D-8F88-4D08FD7ED6B1}"/>
+    <hyperlink ref="F11" r:id="rId45" xr:uid="{E9FA1CD4-77B0-4337-B7D9-41FF5FAF8D5C}"/>
+    <hyperlink ref="G11" r:id="rId46" xr:uid="{44406BDF-4864-4DEE-8D3F-960771AC5EEA}"/>
+    <hyperlink ref="F12" r:id="rId47" xr:uid="{A2470070-51EF-4670-833B-8D482C601671}"/>
+    <hyperlink ref="F13" r:id="rId48" xr:uid="{4D4972B4-0A24-4319-992B-3F7B5C4CCDCE}"/>
+    <hyperlink ref="F14" r:id="rId49" xr:uid="{AE1ACB1F-F85D-4CF3-AC72-FD2F25C8E4B2}"/>
+    <hyperlink ref="D21" r:id="rId50" xr:uid="{6E85802D-CC4C-4BD4-83ED-55100DE115BA}"/>
+    <hyperlink ref="D35" r:id="rId51" xr:uid="{6683E2F8-FB9A-4014-9996-7FEAAC683B93}"/>
+    <hyperlink ref="D36" r:id="rId52" xr:uid="{6AF44C4C-D5AE-4BD7-8C44-C3D0460467C0}"/>
+    <hyperlink ref="D19" r:id="rId53" xr:uid="{80ECF8CD-7A79-402A-B5EC-F9BA63C3B50A}"/>
+    <hyperlink ref="D33" r:id="rId54" xr:uid="{E93DF50E-6385-47B4-B2C7-B9246E51EFC3}"/>
+    <hyperlink ref="D22" r:id="rId55" xr:uid="{13D49606-5D63-4601-9617-2606341647E2}"/>
+    <hyperlink ref="D23" r:id="rId56" xr:uid="{D83D9F73-94C9-4362-9F33-9764794F83C7}"/>
+    <hyperlink ref="D29" r:id="rId57" xr:uid="{7CB307A7-AD29-447B-B87B-FDF01946BA4A}"/>
+    <hyperlink ref="D28" r:id="rId58" xr:uid="{45AB639A-6A68-47E6-820F-5AE96EF37CCE}"/>
+    <hyperlink ref="D27" r:id="rId59" xr:uid="{A6B3F117-56EC-4411-89C5-2B81B32C6D2F}"/>
+    <hyperlink ref="D31" r:id="rId60" xr:uid="{0BEBBA09-865C-426C-A4B4-4F2481A2A4E8}"/>
+    <hyperlink ref="D25" r:id="rId61" xr:uid="{EFEDD41E-1E02-461C-9393-AD2ACCBC2A60}"/>
+    <hyperlink ref="D26" r:id="rId62" xr:uid="{40D3F8D6-8B9A-4507-8102-4BFB0D9B2580}"/>
+    <hyperlink ref="D20" r:id="rId63" xr:uid="{5BA1C18C-D565-4734-9906-9C0A7DC7BFEA}"/>
+    <hyperlink ref="D34" r:id="rId64" xr:uid="{E63D41F9-5B08-43E0-8053-0724E6D37B6B}"/>
+    <hyperlink ref="D18" r:id="rId65" xr:uid="{2D6E9249-18AB-4397-B0F5-437EFBC6F332}"/>
+    <hyperlink ref="D17" r:id="rId66" xr:uid="{6EEDF604-934E-4BBF-844F-1CBB5949AF7F}"/>
+    <hyperlink ref="D16" r:id="rId67" xr:uid="{B21EE433-AA31-44F8-A2B5-B896D27134D4}"/>
+    <hyperlink ref="D32" r:id="rId68" xr:uid="{8D11C5C3-9012-49EE-A7E5-072DFCD7E4CB}"/>
+    <hyperlink ref="D30" r:id="rId69" xr:uid="{99947C2E-DEFB-4F3D-B10B-4C51E1A36A2A}"/>
+    <hyperlink ref="D24" r:id="rId70" xr:uid="{CA6F2ACE-9B39-4D45-9C20-19A5DB6D12CA}"/>
+    <hyperlink ref="F15" r:id="rId71" xr:uid="{C35D8A0A-F10A-40F3-A7C3-C5AA6BBB28B5}"/>
+    <hyperlink ref="F16" r:id="rId72" xr:uid="{AEA8472C-440C-4C92-8A77-FEF9C839BF0D}"/>
+    <hyperlink ref="G16" r:id="rId73" xr:uid="{D288EC2B-5C10-4124-87EF-58A40C745452}"/>
+    <hyperlink ref="H16" r:id="rId74" xr:uid="{AB6F38F4-9CD4-49B8-9315-6A116F3871B3}"/>
+    <hyperlink ref="G17" r:id="rId75" xr:uid="{A5B70704-22DA-478D-9DD9-DCC7AA836C2E}"/>
+    <hyperlink ref="F17" r:id="rId76" xr:uid="{5D05AAA5-6C4E-4951-8A01-ED8966A74C6F}"/>
+    <hyperlink ref="H17" r:id="rId77" xr:uid="{F455D43D-0AE8-4F39-B8B8-A9E496C9515D}"/>
+    <hyperlink ref="F18" r:id="rId78" xr:uid="{5119747E-83D1-43AE-B78D-77BFA9310B65}"/>
+    <hyperlink ref="G18" r:id="rId79" xr:uid="{79EB751C-298E-437E-BEE6-FA6698B99FB9}"/>
+    <hyperlink ref="H18" r:id="rId80" xr:uid="{0509DA5B-CB9D-43F8-8168-2BABDCB86042}"/>
+    <hyperlink ref="I18" r:id="rId81" xr:uid="{ECC362EA-7284-4D5F-961E-DDABCD606149}"/>
+    <hyperlink ref="J18" r:id="rId82" xr:uid="{C4D0C97C-3218-467C-949C-4AE1EBBC383C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Locations.xlsx
+++ b/data/Locations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\landscapingUOB-api\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB9B7452-C7BB-4755-84F4-39E4B7FBFD27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07A53F31-F16E-4DD9-B11C-DDB13E4924B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="263">
   <si>
     <t>Location type</t>
   </si>
@@ -131,24 +131,6 @@
     <t>https://i.postimg.cc/nhJxtzcn/S21.jpg</t>
   </si>
   <si>
-    <t>S22</t>
-  </si>
-  <si>
-    <t>Bahrain Teachers College</t>
-  </si>
-  <si>
-    <t>https://i.postimg.cc/G26b6x5p/S22-7-1.jpg</t>
-  </si>
-  <si>
-    <t>S22A</t>
-  </si>
-  <si>
-    <t>Guidance and Counseling Department</t>
-  </si>
-  <si>
-    <t>https://i.postimg.cc/Vsxq1YhY/S22A-new.jpg</t>
-  </si>
-  <si>
     <t>S23</t>
   </si>
   <si>
@@ -200,9 +182,6 @@
     <t>Deanship of Students' Affairs</t>
   </si>
   <si>
-    <t>https://i.postimg.cc/h40XZTmR/S4-2.jpg</t>
-  </si>
-  <si>
     <t>S40</t>
   </si>
   <si>
@@ -227,18 +206,12 @@
     <t>Transportation Building</t>
   </si>
   <si>
-    <t>https://i.postimg.cc/fbMc1btm/S42-2.jpg</t>
-  </si>
-  <si>
     <t>S43</t>
   </si>
   <si>
     <t>University Press Department</t>
   </si>
   <si>
-    <t>https://i.postimg.cc/3w9XhHm6/S43.jpg</t>
-  </si>
-  <si>
     <t>S44</t>
   </si>
   <si>
@@ -281,51 +254,33 @@
     <t>Classrooms</t>
   </si>
   <si>
-    <t>https://i.postimg.cc/GtTGv8Vw/S48-2.jpg</t>
-  </si>
-  <si>
     <t>S49</t>
   </si>
   <si>
     <t>College of Science Laboratories</t>
   </si>
   <si>
-    <t>https://i.postimg.cc/6TsRc6x7/S49-1.jpg</t>
-  </si>
-  <si>
     <t>S50</t>
   </si>
   <si>
     <t>Al-Haj Hasan Khonji Hall</t>
   </si>
   <si>
-    <t>https://i.postimg.cc/ryZzc5vM/S50.jpg</t>
-  </si>
-  <si>
     <t>S51</t>
   </si>
   <si>
     <t>College of Science and Information Technology Food Outlet</t>
   </si>
   <si>
-    <t>https://i.postimg.cc/yNt4vXxY/S51.jpg</t>
-  </si>
-  <si>
     <t>S52</t>
   </si>
   <si>
-    <t>https://i.postimg.cc/nLdMz7C4/S52.jpg</t>
-  </si>
-  <si>
     <t>S54</t>
   </si>
   <si>
     <t>Assets Department</t>
   </si>
   <si>
-    <t>https://i.postimg.cc/wx1GwWdH/S54-2.jpg</t>
-  </si>
-  <si>
     <t>Business Incubator Center</t>
   </si>
   <si>
@@ -371,9 +326,6 @@
     <t>Western Gate</t>
   </si>
   <si>
-    <t>https://i.postimg.cc/3N3dJJPq/Western-Gate.jpg</t>
-  </si>
-  <si>
     <t>Gate 3-S55</t>
   </si>
   <si>
@@ -455,9 +407,6 @@
     <t>https://i.postimg.cc/TwYSFb5G/S2-Surroundings-2.jpg</t>
   </si>
   <si>
-    <t>https://i.postimg.cc/V6sVVmqm/infrastructure.png</t>
-  </si>
-  <si>
     <t>https://i.postimg.cc/4xgyHSvr/S6.png</t>
   </si>
   <si>
@@ -488,9 +437,6 @@
     <t>https://i.postimg.cc/xjwXGCy2/S39-5-(1).jpg</t>
   </si>
   <si>
-    <t>https://i.postimg.cc/wxC15vc6/S39-3.jpg</t>
-  </si>
-  <si>
     <t>S56, S57</t>
   </si>
   <si>
@@ -516,6 +462,369 @@
   </si>
   <si>
     <t>Gate 3</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/bNYLdq83/S39A.jpg</t>
+  </si>
+  <si>
+    <t>https://postimg.cc/JGf4zshJ</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/W4JcKMfy/Fountain-area-2.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/9fqHSGn5/Fountain-area-5.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/ZqyzgrMh/Fountain-area-7.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/FzXScg21/S40.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/65wRpcrd/S40-5.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/YqJ5F4Sy/S41-8.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/T3V4WCFc/S41-1.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/yddQtBdD/S41-10.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/LX2Qq8nD/S46-1.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/fybHKq7p/S46-2.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/Y0dtLY7q/Behind-Khanji-Hall-1.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/qq1p6yTW/Behind-Khanji-Hall-2.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/gjgGL8pW/Behind-Khanji-Hall-5.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/90LcwZ2V/Behind-Khanji-Hall-8.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/50zvMB4C/S50.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/yxZkKJKy/Behind_S51.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/6QXx0w7J/S51-1.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/K8td4V05/behind-S51-3.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/wvjPfBgG/Behind-S51-4.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/1Xxd9rD7/S56-2.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/7Ytg0YWr/behind-S6-2.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/G2RYdBHT/behind-the-mosque-8.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/DfBs3wFz/behind-the-mosque-10.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/50t4B1GM/fence7.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/rmL9MGrM/S18-2.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/Y2RxBWqw/S18-5.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/fLhvD79Z/S18-6.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/DwnJvCCM/S1A-1.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/ZRB07XqX/Roman-Amphitheater-2.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/Wb2TtQvv/Roman-Amphitheater-5.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/MT7JpY3F/S1B-1.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/4dZFBRwt/S20-2.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/ydBrvCnc/S20-3.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/JhWLVgPD/S20A-1.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/d0KYPX4y/S20A-2.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/W4PvLKXJ/S20A-3.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/Pq8QZVjm/S20B-S20C-Building.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/QMWJ5Y3Q/S20B-S20C-21.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/rptNWZkC/S20B-S20C-26.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/1zNr67Q0/S20B-S20C-31.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/6QNyjMZp/In-Front-of-Health-Clinic-4.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/Gp1H7XD3/In-Front-of-Health-Clinic-9.jpg</t>
+  </si>
+  <si>
+    <t>S22, S22A</t>
+  </si>
+  <si>
+    <t>Bahrain Teachers College, Guidance and Counseling Department</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/L5vb7Qhf/S22-3.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/KjQHVp4M/S22-8.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/6QR1wpyB/S22A-5.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/HL5PHkVW/S22A-7.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/5tqqnYXJ/S23-3.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/bvHH3DZ8/S23-2.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/pd2nV0L1/S24-1.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/cL7nSqdy/S24-2.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/wB6sxWj4/S24-3.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/PrjDFrkQ/S42-7.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/gkWhBkPq/S42-4.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/c4B3qyst/S42-2.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/JhpwShFv/S43-1.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/W45Rx4yH/S43-2.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/DzvkCGx9/S43-3.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/Wz1RWh0R/S44-1.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/FzHtW70X/S44-2.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/6qpsjyCJ/S44-4.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/NF9DjtcL/S48-3.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/brDgwPhy/S48-1.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/yxgj8KHx/S48-4.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/59SL8jPN/S49-4.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/pVJzKy0d/S49-1.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/1RrwD4Wt/S49-2.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/4NK4sShx/S52-2.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/MKcZqFjZ/S52-3.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/NfyGBzr0/S52-5.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/xTSYV1Y3/S54-6.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/3JH7Qx79/S54-7.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/gkPdb2dg/S54-4.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/RVz9xZ9R/S54-8.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/D0pqsM2f/S57-3.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/0jXpmB82/S57-5.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/9QXg5vkz/Boundary-Wall-Main-Gate-11.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/7ZPt8pRh/Boundary-Wall-Main-Gate-8.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/P5fVsB7t/Boundary-Wall-Main-Gate-5.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/BnWZmB7m/Boundary-Wall-Eastern-Gate-4.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/7ZvPKntn/Boundary-Wall-Eastern-Gate-1.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/nh8V3GS9/Boundary-Wall-Eastern-Gate-2.jpghttps://i.postimg.cc/nh8V3GS9/Boundary-Wall-Eastern-Gate-2.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/13xRvr7D/Boundary-Wall-Eastern-Gate-5.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/c1nQ90dX/Running-Track-1.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/449zLsXF/Running-Track-5.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/nVDvRpnd/Running-Track-2.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/ZYdr74J7/Running-Track-7.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/GhNncFW4/S15-4.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/kXZPnQ0R/S15-2.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/zB0XpLVX/main-gate-entrance-2.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/ZRVKj9Cq/Hill-Area-behind-Main-Road-2.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/hjpPMJfh/main-gate-exit.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/HxBs3JVk/main-gate-entrance-8.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/MZ18WfWQ/Western-Gate-2.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/qB2dk6k8/Western-Gate-1.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/jqyrsnsH/Western-Gate-3.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/zBB3sSm6/Eastern-Gate-2.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/633TkLsj/Eastern-Gate-3.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/Y99j5fcT/Eastern-Gate-4.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/RFFQgHg0/S20B-S20C-parks-1.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/bJB0Ww58/S20B-S20C-parks-2.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/bJJHmtmw/S20B-S20C-parks-7.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/qR5cSvF4/S20B-S20C-parks-8.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/2SJMcGYX/S39-parking-1.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/g0mc7Srn/Student-Parking-S39.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/3xgJn5rD/Student-Parking-S39-4.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/dV8t4PQC/Student-Parking-S39-7.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/fLrFCZjr/S40-parks-2.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/tTMfkytm/S40-parks-1.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/Jn2gxmcY/S40-parks-4.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/bJBMg8H5/S40-parks-5.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/Mp9hHyM4/S41-parks-1.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/dV5z38ZM/S41-parks-5.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/nh36rvjN/S41-parks-6.jpg</t>
+  </si>
+  <si>
+    <t>Gate-2-S55</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/MKpF9yWG/Student-Parking-Western-Gate-2.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/FsHBTj9H/Student-Parking-Western-Gate-5.jpg</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/63M71byh/Western-Gate-parks-1.jpg</t>
   </si>
 </sst>
 </file>
@@ -584,7 +893,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -606,7 +915,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -617,6 +925,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -898,7 +1208,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.90625" customWidth="1"/>
@@ -918,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
@@ -927,22 +1237,22 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -965,16 +1275,16 @@
         <v>6</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -997,7 +1307,16 @@
         <v>9</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>134</v>
+        <v>118</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
@@ -1020,7 +1339,13 @@
         <v>12</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>135</v>
+        <v>119</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
@@ -1043,7 +1368,13 @@
         <v>15</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>136</v>
+        <v>120</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -1066,10 +1397,10 @@
         <v>18</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
@@ -1091,6 +1422,12 @@
       <c r="F7" s="8" t="s">
         <v>21</v>
       </c>
+      <c r="G7" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
@@ -1111,6 +1448,15 @@
       <c r="F8" s="8" t="s">
         <v>24</v>
       </c>
+      <c r="G8" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
@@ -1131,6 +1477,18 @@
       <c r="F9" s="8" t="s">
         <v>27</v>
       </c>
+      <c r="G9" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
@@ -1151,28 +1509,43 @@
       <c r="F10" s="8" t="s">
         <v>30</v>
       </c>
+      <c r="G10" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>186</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>187</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>33</v>
+        <v>124</v>
       </c>
       <c r="E11">
-        <v>440</v>
+        <v>545</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>33</v>
+        <v>124</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>141</v>
+        <v>188</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
@@ -1180,19 +1553,25 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E12">
-        <v>105</v>
+        <v>1050</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>36</v>
+        <v>33</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
@@ -1200,19 +1579,28 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E13">
-        <v>1050</v>
+        <v>80</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
@@ -1220,19 +1608,19 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E14">
-        <v>80</v>
+        <v>145</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
@@ -1240,19 +1628,25 @@
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>45</v>
+        <v>125</v>
       </c>
       <c r="E15">
-        <v>145</v>
+        <v>1350</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>45</v>
+        <v>125</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
@@ -1260,25 +1654,25 @@
         <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>142</v>
+        <v>44</v>
       </c>
       <c r="E16">
-        <v>1350</v>
+        <v>175</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>142</v>
+        <v>44</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
@@ -1286,25 +1680,28 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>134</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>135</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E17">
-        <v>175</v>
+        <v>1000</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>146</v>
+        <v>132</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
@@ -1312,31 +1709,28 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>152</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>153</v>
+        <v>47</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>51</v>
+        <v>144</v>
       </c>
       <c r="E18">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>51</v>
+        <v>144</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
@@ -1344,16 +1738,25 @@
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E19">
-        <v>350</v>
+        <v>464</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
@@ -1361,16 +1764,28 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E20">
-        <v>464</v>
+        <v>310</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
@@ -1378,16 +1793,25 @@
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C21" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>60</v>
+        <v>197</v>
       </c>
       <c r="E21">
-        <v>310</v>
+        <v>195</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
@@ -1395,16 +1819,25 @@
         <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C22" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>63</v>
+        <v>202</v>
       </c>
       <c r="E22">
-        <v>195</v>
+        <v>45</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
@@ -1412,16 +1845,28 @@
         <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C23" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E23">
-        <v>45</v>
+        <v>180</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
@@ -1429,73 +1874,94 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E24">
+        <v>90</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E25">
+        <v>150</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C26" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D26" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E24">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>3</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="F26" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" t="s">
         <v>70</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C27" t="s">
         <v>71</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E25">
-        <v>90</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>3</v>
-      </c>
-      <c r="B26" t="s">
-        <v>73</v>
-      </c>
-      <c r="C26" t="s">
-        <v>74</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E26">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>78</v>
+      <c r="D27" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E27">
+        <v>399</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
@@ -1503,16 +1969,25 @@
         <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C28" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>81</v>
+        <v>209</v>
       </c>
       <c r="E28">
-        <v>399</v>
+        <v>163</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
@@ -1520,16 +1995,31 @@
         <v>3</v>
       </c>
       <c r="B29" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>84</v>
+        <v>158</v>
       </c>
       <c r="E29">
-        <v>163</v>
+        <v>194</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
@@ -1537,16 +2027,28 @@
         <v>3</v>
       </c>
       <c r="B30" t="s">
-        <v>85</v>
-      </c>
-      <c r="C30" t="s">
-        <v>86</v>
+        <v>76</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>77</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>87</v>
+        <v>160</v>
       </c>
       <c r="E30">
-        <v>194</v>
+        <v>373</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
@@ -1554,344 +2056,534 @@
         <v>3</v>
       </c>
       <c r="B31" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="E31">
+        <v>161</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="E32" s="6">
+        <v>600</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="I32" s="13" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33" t="s">
+        <v>133</v>
+      </c>
+      <c r="C33" t="s">
+        <v>81</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E33">
+        <v>205</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>3</v>
+      </c>
+      <c r="B34" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" t="s">
+        <v>84</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E34">
+        <v>350</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A35" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B35" t="s">
+        <v>139</v>
+      </c>
+      <c r="C35" t="s">
+        <v>136</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="E35">
+        <v>142</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A36" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B36" t="s">
+        <v>140</v>
+      </c>
+      <c r="C36" t="s">
+        <v>137</v>
+      </c>
+      <c r="D36" s="11"/>
+      <c r="E36" s="10"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A37" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" t="s">
+        <v>141</v>
+      </c>
+      <c r="C37" t="s">
+        <v>138</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="E37" s="10"/>
+      <c r="F37" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>86</v>
+      </c>
+      <c r="B38" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38" t="s">
+        <v>101</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="E38">
+        <v>1300</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C39" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="D39" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="E39" s="6">
+        <v>600</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="H39" s="13" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
         <v>90</v>
       </c>
-      <c r="E31">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>3</v>
-      </c>
-      <c r="B32" t="s">
+      <c r="B40" t="s">
         <v>91</v>
       </c>
-      <c r="C32" t="s">
-        <v>83</v>
-      </c>
-      <c r="D32" s="5" t="s">
+      <c r="C40" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E32">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B33" s="6" t="s">
+      <c r="D40" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="E40">
+        <v>5300</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" t="s">
         <v>94</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="C41" t="s">
         <v>95</v>
       </c>
-      <c r="E33" s="6">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="C34" s="9" t="s">
+      <c r="D41" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E41">
+        <v>16500</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>90</v>
+      </c>
+      <c r="B42" t="s">
         <v>96</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="C42" t="s">
         <v>97</v>
       </c>
-      <c r="E34" s="9">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B35" t="s">
-        <v>98</v>
-      </c>
-      <c r="C35" t="s">
-        <v>99</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="E35">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A36" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="C36" t="s">
-        <v>154</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="E36">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A37" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B37" t="s">
-        <v>158</v>
-      </c>
-      <c r="C37" t="s">
-        <v>155</v>
-      </c>
-      <c r="D37" s="12"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A38" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B38" t="s">
-        <v>159</v>
-      </c>
-      <c r="C38" t="s">
-        <v>156</v>
-      </c>
-      <c r="D38" s="12"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>101</v>
-      </c>
-      <c r="B39" t="s">
-        <v>22</v>
-      </c>
-      <c r="C39" t="s">
-        <v>117</v>
-      </c>
-      <c r="D39" s="12"/>
-      <c r="E39">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="E40" s="6">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>105</v>
-      </c>
-      <c r="B41" t="s">
-        <v>106</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E41">
-        <v>5300</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>105</v>
-      </c>
-      <c r="B42" t="s">
-        <v>109</v>
-      </c>
-      <c r="C42" t="s">
-        <v>110</v>
-      </c>
       <c r="D42" s="5" t="s">
-        <v>111</v>
+        <v>241</v>
       </c>
       <c r="E42">
         <v>16500</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F42" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B43" t="s">
-        <v>112</v>
+        <v>25</v>
       </c>
       <c r="C43" t="s">
-        <v>113</v>
+        <v>26</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>114</v>
+        <v>244</v>
       </c>
       <c r="E43">
-        <v>16500</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+        <v>240</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="B44" t="s">
-        <v>25</v>
+        <v>134</v>
       </c>
       <c r="C44" t="s">
-        <v>26</v>
+        <v>135</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>27</v>
+        <v>249</v>
       </c>
       <c r="E44">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+        <v>400</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="B45" t="s">
-        <v>152</v>
+        <v>48</v>
       </c>
       <c r="C45" t="s">
-        <v>153</v>
+        <v>49</v>
       </c>
       <c r="D45" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="E45">
+        <v>704</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>100</v>
+      </c>
+      <c r="B46" t="s">
         <v>51</v>
       </c>
-      <c r="E45">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>116</v>
-      </c>
-      <c r="B46" t="s">
-        <v>55</v>
-      </c>
       <c r="C46" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>57</v>
+        <v>256</v>
       </c>
       <c r="E46">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+        <v>602</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="B47" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C47" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="E47">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+        <v>128</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="B48" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="C48" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="E48">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+        <v>825</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="B49" t="s">
-        <v>112</v>
+        <v>259</v>
       </c>
       <c r="C49" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E49">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+        <v>262</v>
+      </c>
+      <c r="E49" s="10"/>
+      <c r="F49" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="G49" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="H49" s="14" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>3</v>
       </c>
-      <c r="B50" s="11" t="s">
+      <c r="B50" s="10" t="s">
         <v>10</v>
       </c>
       <c r="C50" t="s">
-        <v>118</v>
-      </c>
-      <c r="D50" s="10"/>
+        <v>102</v>
+      </c>
+      <c r="D50" s="9"/>
       <c r="E50">
         <v>2550</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>119</v>
-      </c>
-      <c r="B51" s="11"/>
+        <v>103</v>
+      </c>
+      <c r="B51" s="10"/>
       <c r="C51" t="s">
-        <v>120</v>
-      </c>
-      <c r="D51" s="10"/>
+        <v>104</v>
+      </c>
+      <c r="D51" s="9"/>
       <c r="E51">
         <v>13500</v>
       </c>
     </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="G57" s="8"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D43">
-    <sortCondition ref="A2:A43"/>
-    <sortCondition ref="B2:B43"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D42">
+    <sortCondition ref="A2:A42"/>
+    <sortCondition ref="B2:B42"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
@@ -1901,87 +2593,214 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="D5" r:id="rId1" xr:uid="{80EE9128-EF22-45E1-A050-B4A922D7A5A4}"/>
-    <hyperlink ref="D15" r:id="rId2" xr:uid="{892A1EEC-B028-4BF1-ADCD-AF96A0988B50}"/>
+    <hyperlink ref="D14" r:id="rId2" xr:uid="{892A1EEC-B028-4BF1-ADCD-AF96A0988B50}"/>
     <hyperlink ref="D10" r:id="rId3" xr:uid="{F1426B06-7CBB-4D59-AE83-B095FA6474E2}"/>
     <hyperlink ref="D8" r:id="rId4" xr:uid="{592D78FC-336C-471A-91BD-1562E94DA284}"/>
     <hyperlink ref="D9" r:id="rId5" xr:uid="{A2D386D9-0502-4921-BB61-A819FF837370}"/>
-    <hyperlink ref="D13" r:id="rId6" xr:uid="{5A89EF2A-F868-480F-9E72-4F25C74088A4}"/>
+    <hyperlink ref="D12" r:id="rId6" xr:uid="{5A89EF2A-F868-480F-9E72-4F25C74088A4}"/>
     <hyperlink ref="D2" r:id="rId7" xr:uid="{6CF4DEC1-CD4E-4844-A06E-A3B5553E4A0A}"/>
     <hyperlink ref="D3" r:id="rId8" xr:uid="{9E806015-46CC-43F4-B15B-0F80E18DD0D3}"/>
     <hyperlink ref="D4" r:id="rId9" xr:uid="{0BE1B822-D34C-40EF-8B0F-F98C95A68F23}"/>
     <hyperlink ref="D11" r:id="rId10" xr:uid="{BD02D7C7-CF92-4415-BD68-A5E1CD860AB5}"/>
-    <hyperlink ref="D14" r:id="rId11" xr:uid="{E2D6E56A-BEDF-4371-A57A-AE46E0B0D271}"/>
-    <hyperlink ref="D12" r:id="rId12" xr:uid="{9B82FEF9-0E16-4B92-A3E1-1FC2CB2AF171}"/>
-    <hyperlink ref="D7" r:id="rId13" xr:uid="{2ED0409A-8763-4061-A855-6C9AC6A9D6BD}"/>
-    <hyperlink ref="D40" r:id="rId14" xr:uid="{887D03B3-F5B5-4EC3-B378-CFF1ACACC697}"/>
-    <hyperlink ref="D41" r:id="rId15" xr:uid="{25328B39-D4E0-444C-9000-8F992DB7BA09}"/>
-    <hyperlink ref="D43" r:id="rId16" xr:uid="{6B7E0906-BF85-4BF1-A5E5-9F4F8AB12E12}"/>
-    <hyperlink ref="D42" r:id="rId17" xr:uid="{A757999D-BA12-4BC4-B318-11BE5E932894}"/>
-    <hyperlink ref="D6" r:id="rId18" xr:uid="{705A06BF-AD9E-4AEF-8BEC-6580A15197D6}"/>
-    <hyperlink ref="D44" r:id="rId19" xr:uid="{F581F61C-236D-49A3-AE06-C2A7FF968C89}"/>
-    <hyperlink ref="D45" r:id="rId20" xr:uid="{BB91F514-736D-4FC9-A32E-788A20E577B9}"/>
-    <hyperlink ref="D46" r:id="rId21" xr:uid="{A36D56AA-7C90-4154-A870-DA9409189D1F}"/>
-    <hyperlink ref="D47" r:id="rId22" xr:uid="{00DDF648-5623-4E1D-8FC4-42D38FAEE4CA}"/>
-    <hyperlink ref="D48" r:id="rId23" xr:uid="{77EAAAD6-086C-4DCF-9B24-E59430A2E2FB}"/>
-    <hyperlink ref="D49" r:id="rId24" xr:uid="{CE8A3876-BF7A-4C23-95FB-161481F8F980}"/>
-    <hyperlink ref="F25" r:id="rId25" xr:uid="{E4CD215B-218A-44EC-9945-5F6AD197B3B2}"/>
-    <hyperlink ref="G25" r:id="rId26" xr:uid="{522CE0D5-7681-455E-9A32-6774CD570260}"/>
-    <hyperlink ref="H25" r:id="rId27" xr:uid="{A440C7F8-BC12-4ED8-80D1-5687F587FDDF}"/>
-    <hyperlink ref="G2" r:id="rId28" xr:uid="{E92EE150-871A-439E-974B-FA2049C8CA38}"/>
-    <hyperlink ref="H2" r:id="rId29" xr:uid="{03D46786-9004-478B-A395-4AA7EF082A56}"/>
-    <hyperlink ref="I2" r:id="rId30" xr:uid="{57A7AAAC-E898-44F4-A3B0-AF97E1EBFE69}"/>
-    <hyperlink ref="J2" r:id="rId31" xr:uid="{ACBBE8A2-CC26-4054-A6DA-6E5C07960AD1}"/>
-    <hyperlink ref="F3" r:id="rId32" xr:uid="{29114336-215A-43FA-8297-CDDD761C1501}"/>
-    <hyperlink ref="G3" r:id="rId33" xr:uid="{0AE835A0-8DDB-4A91-8176-2AFF9C2AEA07}"/>
-    <hyperlink ref="F4" r:id="rId34" xr:uid="{9F1D3B58-9986-4688-ABF5-8FF2375FBF82}"/>
-    <hyperlink ref="G4" r:id="rId35" xr:uid="{6CB43155-6638-4798-B491-DB6FA525EB50}"/>
-    <hyperlink ref="F5" r:id="rId36" xr:uid="{7DCFF457-0664-4586-B064-437E516400A0}"/>
-    <hyperlink ref="G5" r:id="rId37" xr:uid="{343CFCD0-DE46-476D-8E81-253A8E3B316C}"/>
-    <hyperlink ref="F6" r:id="rId38" xr:uid="{3EC21E9D-842C-4CB8-B811-D23F2C778BF7}"/>
-    <hyperlink ref="G6" r:id="rId39" xr:uid="{33FCB128-9197-43CE-8CB7-FE8F3059BE4F}"/>
-    <hyperlink ref="H6" r:id="rId40" xr:uid="{1F8966A1-2290-4CEF-BB02-FC990CD8D791}"/>
-    <hyperlink ref="F7" r:id="rId41" xr:uid="{423CFF82-45DF-4D68-BB50-979F20779C0F}"/>
-    <hyperlink ref="F8" r:id="rId42" xr:uid="{E5CBA92A-AB4F-478A-9CFE-9419577F0ED5}"/>
-    <hyperlink ref="F10" r:id="rId43" xr:uid="{EB116F53-35BE-4168-A3B3-A6B7F3013480}"/>
-    <hyperlink ref="F9" r:id="rId44" xr:uid="{AAFC07D3-B9CC-483D-8F88-4D08FD7ED6B1}"/>
-    <hyperlink ref="F11" r:id="rId45" xr:uid="{E9FA1CD4-77B0-4337-B7D9-41FF5FAF8D5C}"/>
-    <hyperlink ref="G11" r:id="rId46" xr:uid="{44406BDF-4864-4DEE-8D3F-960771AC5EEA}"/>
-    <hyperlink ref="F12" r:id="rId47" xr:uid="{A2470070-51EF-4670-833B-8D482C601671}"/>
-    <hyperlink ref="F13" r:id="rId48" xr:uid="{4D4972B4-0A24-4319-992B-3F7B5C4CCDCE}"/>
-    <hyperlink ref="F14" r:id="rId49" xr:uid="{AE1ACB1F-F85D-4CF3-AC72-FD2F25C8E4B2}"/>
-    <hyperlink ref="D21" r:id="rId50" xr:uid="{6E85802D-CC4C-4BD4-83ED-55100DE115BA}"/>
-    <hyperlink ref="D35" r:id="rId51" xr:uid="{6683E2F8-FB9A-4014-9996-7FEAAC683B93}"/>
-    <hyperlink ref="D36" r:id="rId52" xr:uid="{6AF44C4C-D5AE-4BD7-8C44-C3D0460467C0}"/>
-    <hyperlink ref="D19" r:id="rId53" xr:uid="{80ECF8CD-7A79-402A-B5EC-F9BA63C3B50A}"/>
-    <hyperlink ref="D33" r:id="rId54" xr:uid="{E93DF50E-6385-47B4-B2C7-B9246E51EFC3}"/>
-    <hyperlink ref="D22" r:id="rId55" xr:uid="{13D49606-5D63-4601-9617-2606341647E2}"/>
-    <hyperlink ref="D23" r:id="rId56" xr:uid="{D83D9F73-94C9-4362-9F33-9764794F83C7}"/>
-    <hyperlink ref="D29" r:id="rId57" xr:uid="{7CB307A7-AD29-447B-B87B-FDF01946BA4A}"/>
-    <hyperlink ref="D28" r:id="rId58" xr:uid="{45AB639A-6A68-47E6-820F-5AE96EF37CCE}"/>
-    <hyperlink ref="D27" r:id="rId59" xr:uid="{A6B3F117-56EC-4411-89C5-2B81B32C6D2F}"/>
-    <hyperlink ref="D31" r:id="rId60" xr:uid="{0BEBBA09-865C-426C-A4B4-4F2481A2A4E8}"/>
-    <hyperlink ref="D25" r:id="rId61" xr:uid="{EFEDD41E-1E02-461C-9393-AD2ACCBC2A60}"/>
-    <hyperlink ref="D26" r:id="rId62" xr:uid="{40D3F8D6-8B9A-4507-8102-4BFB0D9B2580}"/>
-    <hyperlink ref="D20" r:id="rId63" xr:uid="{5BA1C18C-D565-4734-9906-9C0A7DC7BFEA}"/>
-    <hyperlink ref="D34" r:id="rId64" xr:uid="{E63D41F9-5B08-43E0-8053-0724E6D37B6B}"/>
-    <hyperlink ref="D18" r:id="rId65" xr:uid="{2D6E9249-18AB-4397-B0F5-437EFBC6F332}"/>
-    <hyperlink ref="D17" r:id="rId66" xr:uid="{6EEDF604-934E-4BBF-844F-1CBB5949AF7F}"/>
-    <hyperlink ref="D16" r:id="rId67" xr:uid="{B21EE433-AA31-44F8-A2B5-B896D27134D4}"/>
-    <hyperlink ref="D32" r:id="rId68" xr:uid="{8D11C5C3-9012-49EE-A7E5-072DFCD7E4CB}"/>
-    <hyperlink ref="D30" r:id="rId69" xr:uid="{99947C2E-DEFB-4F3D-B10B-4C51E1A36A2A}"/>
-    <hyperlink ref="D24" r:id="rId70" xr:uid="{CA6F2ACE-9B39-4D45-9C20-19A5DB6D12CA}"/>
-    <hyperlink ref="F15" r:id="rId71" xr:uid="{C35D8A0A-F10A-40F3-A7C3-C5AA6BBB28B5}"/>
-    <hyperlink ref="F16" r:id="rId72" xr:uid="{AEA8472C-440C-4C92-8A77-FEF9C839BF0D}"/>
-    <hyperlink ref="G16" r:id="rId73" xr:uid="{D288EC2B-5C10-4124-87EF-58A40C745452}"/>
-    <hyperlink ref="H16" r:id="rId74" xr:uid="{AB6F38F4-9CD4-49B8-9315-6A116F3871B3}"/>
-    <hyperlink ref="G17" r:id="rId75" xr:uid="{A5B70704-22DA-478D-9DD9-DCC7AA836C2E}"/>
-    <hyperlink ref="F17" r:id="rId76" xr:uid="{5D05AAA5-6C4E-4951-8A01-ED8966A74C6F}"/>
-    <hyperlink ref="H17" r:id="rId77" xr:uid="{F455D43D-0AE8-4F39-B8B8-A9E496C9515D}"/>
-    <hyperlink ref="F18" r:id="rId78" xr:uid="{5119747E-83D1-43AE-B78D-77BFA9310B65}"/>
-    <hyperlink ref="G18" r:id="rId79" xr:uid="{79EB751C-298E-437E-BEE6-FA6698B99FB9}"/>
-    <hyperlink ref="H18" r:id="rId80" xr:uid="{0509DA5B-CB9D-43F8-8168-2BABDCB86042}"/>
-    <hyperlink ref="I18" r:id="rId81" xr:uid="{ECC362EA-7284-4D5F-961E-DDABCD606149}"/>
-    <hyperlink ref="J18" r:id="rId82" xr:uid="{C4D0C97C-3218-467C-949C-4AE1EBBC383C}"/>
+    <hyperlink ref="D13" r:id="rId11" xr:uid="{E2D6E56A-BEDF-4371-A57A-AE46E0B0D271}"/>
+    <hyperlink ref="D7" r:id="rId12" xr:uid="{2ED0409A-8763-4061-A855-6C9AC6A9D6BD}"/>
+    <hyperlink ref="D39" r:id="rId13" xr:uid="{887D03B3-F5B5-4EC3-B378-CFF1ACACC697}"/>
+    <hyperlink ref="D40" r:id="rId14" xr:uid="{25328B39-D4E0-444C-9000-8F992DB7BA09}"/>
+    <hyperlink ref="D42" r:id="rId15" xr:uid="{6B7E0906-BF85-4BF1-A5E5-9F4F8AB12E12}"/>
+    <hyperlink ref="D41" r:id="rId16" xr:uid="{A757999D-BA12-4BC4-B318-11BE5E932894}"/>
+    <hyperlink ref="D6" r:id="rId17" xr:uid="{705A06BF-AD9E-4AEF-8BEC-6580A15197D6}"/>
+    <hyperlink ref="D43" r:id="rId18" xr:uid="{F581F61C-236D-49A3-AE06-C2A7FF968C89}"/>
+    <hyperlink ref="D44" r:id="rId19" xr:uid="{BB91F514-736D-4FC9-A32E-788A20E577B9}"/>
+    <hyperlink ref="D45" r:id="rId20" xr:uid="{A36D56AA-7C90-4154-A870-DA9409189D1F}"/>
+    <hyperlink ref="D46" r:id="rId21" xr:uid="{00DDF648-5623-4E1D-8FC4-42D38FAEE4CA}"/>
+    <hyperlink ref="D47" r:id="rId22" xr:uid="{77EAAAD6-086C-4DCF-9B24-E59430A2E2FB}"/>
+    <hyperlink ref="D48" r:id="rId23" xr:uid="{CE8A3876-BF7A-4C23-95FB-161481F8F980}"/>
+    <hyperlink ref="F24" r:id="rId24" xr:uid="{E4CD215B-218A-44EC-9945-5F6AD197B3B2}"/>
+    <hyperlink ref="G24" r:id="rId25" xr:uid="{522CE0D5-7681-455E-9A32-6774CD570260}"/>
+    <hyperlink ref="H24" r:id="rId26" xr:uid="{A440C7F8-BC12-4ED8-80D1-5687F587FDDF}"/>
+    <hyperlink ref="G2" r:id="rId27" xr:uid="{E92EE150-871A-439E-974B-FA2049C8CA38}"/>
+    <hyperlink ref="H2" r:id="rId28" xr:uid="{03D46786-9004-478B-A395-4AA7EF082A56}"/>
+    <hyperlink ref="I2" r:id="rId29" xr:uid="{57A7AAAC-E898-44F4-A3B0-AF97E1EBFE69}"/>
+    <hyperlink ref="J2" r:id="rId30" xr:uid="{ACBBE8A2-CC26-4054-A6DA-6E5C07960AD1}"/>
+    <hyperlink ref="F3" r:id="rId31" xr:uid="{29114336-215A-43FA-8297-CDDD761C1501}"/>
+    <hyperlink ref="G3" r:id="rId32" xr:uid="{0AE835A0-8DDB-4A91-8176-2AFF9C2AEA07}"/>
+    <hyperlink ref="F4" r:id="rId33" xr:uid="{9F1D3B58-9986-4688-ABF5-8FF2375FBF82}"/>
+    <hyperlink ref="G4" r:id="rId34" xr:uid="{6CB43155-6638-4798-B491-DB6FA525EB50}"/>
+    <hyperlink ref="F5" r:id="rId35" xr:uid="{7DCFF457-0664-4586-B064-437E516400A0}"/>
+    <hyperlink ref="G5" r:id="rId36" xr:uid="{343CFCD0-DE46-476D-8E81-253A8E3B316C}"/>
+    <hyperlink ref="F6" r:id="rId37" xr:uid="{3EC21E9D-842C-4CB8-B811-D23F2C778BF7}"/>
+    <hyperlink ref="G6" r:id="rId38" xr:uid="{33FCB128-9197-43CE-8CB7-FE8F3059BE4F}"/>
+    <hyperlink ref="H6" r:id="rId39" xr:uid="{1F8966A1-2290-4CEF-BB02-FC990CD8D791}"/>
+    <hyperlink ref="F7" r:id="rId40" xr:uid="{423CFF82-45DF-4D68-BB50-979F20779C0F}"/>
+    <hyperlink ref="F8" r:id="rId41" xr:uid="{E5CBA92A-AB4F-478A-9CFE-9419577F0ED5}"/>
+    <hyperlink ref="F10" r:id="rId42" xr:uid="{EB116F53-35BE-4168-A3B3-A6B7F3013480}"/>
+    <hyperlink ref="F9" r:id="rId43" xr:uid="{AAFC07D3-B9CC-483D-8F88-4D08FD7ED6B1}"/>
+    <hyperlink ref="F12" r:id="rId44" xr:uid="{4D4972B4-0A24-4319-992B-3F7B5C4CCDCE}"/>
+    <hyperlink ref="F13" r:id="rId45" xr:uid="{AE1ACB1F-F85D-4CF3-AC72-FD2F25C8E4B2}"/>
+    <hyperlink ref="D20" r:id="rId46" xr:uid="{6E85802D-CC4C-4BD4-83ED-55100DE115BA}"/>
+    <hyperlink ref="D34" r:id="rId47" xr:uid="{6683E2F8-FB9A-4014-9996-7FEAAC683B93}"/>
+    <hyperlink ref="D18" r:id="rId48" xr:uid="{80ECF8CD-7A79-402A-B5EC-F9BA63C3B50A}"/>
+    <hyperlink ref="D32" r:id="rId49" xr:uid="{E93DF50E-6385-47B4-B2C7-B9246E51EFC3}"/>
+    <hyperlink ref="D21" r:id="rId50" xr:uid="{13D49606-5D63-4601-9617-2606341647E2}"/>
+    <hyperlink ref="D22" r:id="rId51" xr:uid="{D83D9F73-94C9-4362-9F33-9764794F83C7}"/>
+    <hyperlink ref="D28" r:id="rId52" xr:uid="{7CB307A7-AD29-447B-B87B-FDF01946BA4A}"/>
+    <hyperlink ref="D27" r:id="rId53" xr:uid="{45AB639A-6A68-47E6-820F-5AE96EF37CCE}"/>
+    <hyperlink ref="D26" r:id="rId54" xr:uid="{A6B3F117-56EC-4411-89C5-2B81B32C6D2F}"/>
+    <hyperlink ref="D30" r:id="rId55" xr:uid="{0BEBBA09-865C-426C-A4B4-4F2481A2A4E8}"/>
+    <hyperlink ref="D24" r:id="rId56" xr:uid="{EFEDD41E-1E02-461C-9393-AD2ACCBC2A60}"/>
+    <hyperlink ref="D25" r:id="rId57" xr:uid="{40D3F8D6-8B9A-4507-8102-4BFB0D9B2580}"/>
+    <hyperlink ref="D19" r:id="rId58" xr:uid="{5BA1C18C-D565-4734-9906-9C0A7DC7BFEA}"/>
+    <hyperlink ref="D33" r:id="rId59" xr:uid="{E63D41F9-5B08-43E0-8053-0724E6D37B6B}"/>
+    <hyperlink ref="D17" r:id="rId60" xr:uid="{2D6E9249-18AB-4397-B0F5-437EFBC6F332}"/>
+    <hyperlink ref="D16" r:id="rId61" xr:uid="{6EEDF604-934E-4BBF-844F-1CBB5949AF7F}"/>
+    <hyperlink ref="D15" r:id="rId62" xr:uid="{B21EE433-AA31-44F8-A2B5-B896D27134D4}"/>
+    <hyperlink ref="D31" r:id="rId63" xr:uid="{8D11C5C3-9012-49EE-A7E5-072DFCD7E4CB}"/>
+    <hyperlink ref="D29" r:id="rId64" xr:uid="{99947C2E-DEFB-4F3D-B10B-4C51E1A36A2A}"/>
+    <hyperlink ref="D23" r:id="rId65" xr:uid="{CA6F2ACE-9B39-4D45-9C20-19A5DB6D12CA}"/>
+    <hyperlink ref="F14" r:id="rId66" xr:uid="{C35D8A0A-F10A-40F3-A7C3-C5AA6BBB28B5}"/>
+    <hyperlink ref="F15" r:id="rId67" xr:uid="{AEA8472C-440C-4C92-8A77-FEF9C839BF0D}"/>
+    <hyperlink ref="G15" r:id="rId68" xr:uid="{D288EC2B-5C10-4124-87EF-58A40C745452}"/>
+    <hyperlink ref="H15" r:id="rId69" xr:uid="{AB6F38F4-9CD4-49B8-9315-6A116F3871B3}"/>
+    <hyperlink ref="G16" r:id="rId70" xr:uid="{A5B70704-22DA-478D-9DD9-DCC7AA836C2E}"/>
+    <hyperlink ref="F16" r:id="rId71" xr:uid="{5D05AAA5-6C4E-4951-8A01-ED8966A74C6F}"/>
+    <hyperlink ref="H16" r:id="rId72" xr:uid="{F455D43D-0AE8-4F39-B8B8-A9E496C9515D}"/>
+    <hyperlink ref="F17" r:id="rId73" xr:uid="{79EB751C-298E-437E-BEE6-FA6698B99FB9}"/>
+    <hyperlink ref="G17" r:id="rId74" xr:uid="{0509DA5B-CB9D-43F8-8168-2BABDCB86042}"/>
+    <hyperlink ref="H17" r:id="rId75" xr:uid="{ECC362EA-7284-4D5F-961E-DDABCD606149}"/>
+    <hyperlink ref="I17" r:id="rId76" xr:uid="{C4D0C97C-3218-467C-949C-4AE1EBBC383C}"/>
+    <hyperlink ref="F18" r:id="rId77" xr:uid="{05C1816A-2036-4439-96E0-F98D7F259359}"/>
+    <hyperlink ref="G18" r:id="rId78" xr:uid="{11C8AB28-D288-44B1-BCDB-A0C61F053B02}"/>
+    <hyperlink ref="H18" r:id="rId79" xr:uid="{FF4F91CD-AE0A-4A81-9A51-52876A3DDD43}"/>
+    <hyperlink ref="I18" r:id="rId80" xr:uid="{4299A509-749B-4437-81D2-6C77C1C5AF1E}"/>
+    <hyperlink ref="G19" r:id="rId81" xr:uid="{55C014BF-66B6-4706-85C0-84540030B50B}"/>
+    <hyperlink ref="H19" r:id="rId82" xr:uid="{2C895605-0051-41E9-B08B-83568DE5602A}"/>
+    <hyperlink ref="F19" r:id="rId83" xr:uid="{58DB5816-73D7-4204-B0DF-6EBF658657DE}"/>
+    <hyperlink ref="F20" r:id="rId84" xr:uid="{0A66D999-EA69-47C8-A2AC-299DD5FBF010}"/>
+    <hyperlink ref="G20" r:id="rId85" xr:uid="{97F6E9F1-52E1-4EBE-8DFF-65A4B3FA9E36}"/>
+    <hyperlink ref="H20" r:id="rId86" xr:uid="{BA0089AB-0C4F-47D6-96E0-392E1053B09F}"/>
+    <hyperlink ref="I20" r:id="rId87" xr:uid="{A9F10709-59FD-4282-B75A-7EE822564D38}"/>
+    <hyperlink ref="F21" r:id="rId88" xr:uid="{21B61173-201D-47B9-AEA4-D94F1EA6AD81}"/>
+    <hyperlink ref="F22" r:id="rId89" xr:uid="{09E4616E-ACC3-481C-B7BB-CFC12F88739D}"/>
+    <hyperlink ref="F23" r:id="rId90" xr:uid="{1089B129-D695-4723-B494-CF0477A9644D}"/>
+    <hyperlink ref="F25" r:id="rId91" xr:uid="{2F053FA1-B410-4F73-8547-0F2B33DC76A9}"/>
+    <hyperlink ref="G25" r:id="rId92" xr:uid="{D31249E2-8233-4A00-85AD-891DC893A2FC}"/>
+    <hyperlink ref="H25" r:id="rId93" xr:uid="{F9C52003-5F22-4C0E-BC6F-6AC71B56FADE}"/>
+    <hyperlink ref="F26" r:id="rId94" xr:uid="{A7082986-43F1-48A4-966A-2F8749DE459A}"/>
+    <hyperlink ref="F27" r:id="rId95" xr:uid="{FC541651-8258-4B65-89E4-2086DBDCC35A}"/>
+    <hyperlink ref="F28" r:id="rId96" xr:uid="{6536A816-A07F-44C4-AE5B-DDB36A10C883}"/>
+    <hyperlink ref="G29" r:id="rId97" xr:uid="{C97F3C71-A881-44A7-BE39-456500CD6646}"/>
+    <hyperlink ref="H29" r:id="rId98" xr:uid="{B9D37DC0-2755-477C-9CB7-6561F246BE18}"/>
+    <hyperlink ref="I29" r:id="rId99" xr:uid="{B1E4F314-A147-4F40-8C9D-EFAA0AA703D1}"/>
+    <hyperlink ref="J29" r:id="rId100" xr:uid="{C9608237-ADA3-4C14-99BE-5C1BE86163B1}"/>
+    <hyperlink ref="F29" r:id="rId101" xr:uid="{3CAED30C-63B4-4055-9578-D5B8D1BF52BE}"/>
+    <hyperlink ref="G30" r:id="rId102" xr:uid="{2889809D-2765-4B4A-B8DE-1FAB97E5397E}"/>
+    <hyperlink ref="F30" r:id="rId103" xr:uid="{0B7D0125-8B26-4F73-A9F3-4EB01DD1DC2A}"/>
+    <hyperlink ref="H30" r:id="rId104" xr:uid="{E59F1A09-2392-4CEE-9909-713123B2BAE3}"/>
+    <hyperlink ref="I30" r:id="rId105" xr:uid="{DB189F7C-BA2F-4C6D-953A-DBE427906884}"/>
+    <hyperlink ref="F31" r:id="rId106" xr:uid="{84AC6B8F-3DE2-488D-8E3E-2E4C1453E375}"/>
+    <hyperlink ref="F32" r:id="rId107" xr:uid="{B0E3430A-C915-4A0B-BD3E-5DEB3A28BC13}"/>
+    <hyperlink ref="G33" r:id="rId108" xr:uid="{C5E0A2AF-1728-403C-A8AF-2D44268055AB}"/>
+    <hyperlink ref="F33" r:id="rId109" xr:uid="{05C5A534-25A3-4BD5-9612-1FF81718F9A3}"/>
+    <hyperlink ref="F34" r:id="rId110" xr:uid="{31C999EC-6BE8-4CA4-BABA-AD0174C3DFC7}"/>
+    <hyperlink ref="G34" r:id="rId111" xr:uid="{8D62F4B5-6EA6-4B21-BFC2-804D90BDBDC8}"/>
+    <hyperlink ref="H34" r:id="rId112" xr:uid="{4E20A5CF-7B0B-4507-AD6C-F93C28E30DF8}"/>
+    <hyperlink ref="I34" r:id="rId113" xr:uid="{E19D879F-0681-4FF1-B4CF-778D01985C9A}"/>
+    <hyperlink ref="G35" r:id="rId114" xr:uid="{28838D67-4269-48C8-A701-B02B96D91311}"/>
+    <hyperlink ref="F39" r:id="rId115" xr:uid="{46881E06-AF3E-4498-90A6-5603AF757E23}"/>
+    <hyperlink ref="F40" r:id="rId116" xr:uid="{727B03F7-9A8B-4DA3-9D29-5596B267EE95}"/>
+    <hyperlink ref="F41" r:id="rId117" xr:uid="{9B6DC96C-7D15-4E97-A0A2-3212543AD8C2}"/>
+    <hyperlink ref="F42" r:id="rId118" xr:uid="{86BA4F64-EF0F-452D-8BD7-5EA5D58CA18A}"/>
+    <hyperlink ref="F43" r:id="rId119" xr:uid="{0E9CAB7A-97FE-41FF-A8D6-0F1039FF38B5}"/>
+    <hyperlink ref="F45" r:id="rId120" xr:uid="{167ADD63-BA3C-4A90-B320-DDE349E0FFCE}"/>
+    <hyperlink ref="F46" r:id="rId121" xr:uid="{4E3D1917-3F6F-4CC2-9329-0E2F3CC2B127}"/>
+    <hyperlink ref="F47" r:id="rId122" xr:uid="{E3857A39-84C9-4355-B386-2116B93F2AF2}"/>
+    <hyperlink ref="F48" r:id="rId123" xr:uid="{38404B29-83A5-44D1-8FCD-8B6F32BBCC61}"/>
+    <hyperlink ref="H3" r:id="rId124" xr:uid="{D7ACE3D7-0909-4358-89EB-E203F74D01DD}"/>
+    <hyperlink ref="I3" r:id="rId125" xr:uid="{4C57E6C0-950A-4F6B-935D-9C68358C8DAA}"/>
+    <hyperlink ref="J3" r:id="rId126" xr:uid="{92574A9A-8B93-4490-B957-1B5176348D43}"/>
+    <hyperlink ref="H4" r:id="rId127" xr:uid="{5D2722C9-7266-4528-8640-4432737946A5}"/>
+    <hyperlink ref="I4" r:id="rId128" xr:uid="{6F264713-6792-46A2-A37A-394CFDF5B1D3}"/>
+    <hyperlink ref="I5" r:id="rId129" xr:uid="{57063407-0DE1-471C-A419-6D8B0254303B}"/>
+    <hyperlink ref="H5" r:id="rId130" xr:uid="{C6D7BD0C-E8F9-4067-BD15-3E5D816A2558}"/>
+    <hyperlink ref="G7" r:id="rId131" xr:uid="{A1187DE1-373D-4EB3-B77A-300F84871F08}"/>
+    <hyperlink ref="H7" r:id="rId132" xr:uid="{D38DF95C-D70A-4848-ABFF-19E789361B72}"/>
+    <hyperlink ref="G8" r:id="rId133" xr:uid="{9EFE23B3-FC99-41F7-AC45-A9DDFE524163}"/>
+    <hyperlink ref="I8" r:id="rId134" xr:uid="{0EBBB594-37E9-45C2-8996-7D3CA2CC0C44}"/>
+    <hyperlink ref="H8" r:id="rId135" xr:uid="{78001BA6-E0B8-4A38-8E12-7C9DCB2F6335}"/>
+    <hyperlink ref="G9" r:id="rId136" xr:uid="{F0CA61D1-3FD4-487D-8F4E-DD350052FB38}"/>
+    <hyperlink ref="H9" r:id="rId137" xr:uid="{CAF22B94-3D99-4B7E-A738-FD81446692BB}"/>
+    <hyperlink ref="I9" r:id="rId138" xr:uid="{B450B764-93AC-417B-A282-5A8346EAE1A7}"/>
+    <hyperlink ref="J9" r:id="rId139" xr:uid="{704C5BBF-8BE2-4420-A166-AC2CD7AD1E91}"/>
+    <hyperlink ref="G10" r:id="rId140" xr:uid="{49BE4D67-D899-447A-869B-A753A7EF1DCE}"/>
+    <hyperlink ref="H10" r:id="rId141" xr:uid="{C90E7906-AEBB-4ABE-9D03-AC868FE51834}"/>
+    <hyperlink ref="F11" r:id="rId142" xr:uid="{CD8BC463-A6FD-47D3-A6BE-8541C7B17F8C}"/>
+    <hyperlink ref="G11" r:id="rId143" xr:uid="{F6697460-4CDE-40CF-8566-B9678CC757A3}"/>
+    <hyperlink ref="H11" r:id="rId144" xr:uid="{9B5DCC2B-6981-4DD9-AF64-389DE9092B96}"/>
+    <hyperlink ref="I11" r:id="rId145" xr:uid="{DA699BD6-CAEE-416E-8F1D-A55C36C56AE4}"/>
+    <hyperlink ref="J11" r:id="rId146" xr:uid="{A7BD3FC2-C8DC-4733-9410-42284DA4F1F6}"/>
+    <hyperlink ref="H12" r:id="rId147" xr:uid="{0FC4AF10-024B-4935-A432-123F99676C86}"/>
+    <hyperlink ref="G12" r:id="rId148" xr:uid="{6B203EB9-F9C5-4DF3-958E-A960F4803AE1}"/>
+    <hyperlink ref="G13" r:id="rId149" xr:uid="{B4761B14-C746-4E1C-B0CC-4282242C6C5F}"/>
+    <hyperlink ref="H13" r:id="rId150" xr:uid="{CCC22BB1-946A-4B24-9A64-DA351077FB0F}"/>
+    <hyperlink ref="I13" r:id="rId151" xr:uid="{E0B17EDD-8BA2-452F-BBAC-F17C496E83AB}"/>
+    <hyperlink ref="H21" r:id="rId152" xr:uid="{2E36CE09-712F-4AD5-B96D-8370E61F31B3}"/>
+    <hyperlink ref="G21" r:id="rId153" xr:uid="{B055E6F4-CA9F-4555-9276-CF8F2A45B6D9}"/>
+    <hyperlink ref="G22" r:id="rId154" xr:uid="{AA4133E7-3889-43CD-9F2E-C2C47F22E400}"/>
+    <hyperlink ref="H22" r:id="rId155" xr:uid="{3A5DCC72-C5D4-4BCF-8039-2C2AE919C075}"/>
+    <hyperlink ref="G23" r:id="rId156" xr:uid="{10330557-E54B-4B9B-86A0-41CD4825CE6E}"/>
+    <hyperlink ref="H23" r:id="rId157" xr:uid="{914480F3-2888-48A2-A674-CC244D63CAC1}"/>
+    <hyperlink ref="I23" r:id="rId158" xr:uid="{1354A895-A264-45D3-BB7E-3AC13C7221DB}"/>
+    <hyperlink ref="G27" r:id="rId159" xr:uid="{2462FC32-31D3-4141-BEB0-4EDBF7FBEDD6}"/>
+    <hyperlink ref="H27" r:id="rId160" xr:uid="{7DACD8F1-8870-4FBB-AAD7-76D21697341F}"/>
+    <hyperlink ref="G28" r:id="rId161" xr:uid="{1616BF2F-456C-488F-B3C2-978846270839}"/>
+    <hyperlink ref="H28" r:id="rId162" xr:uid="{5F290872-5217-46C4-80B2-F15A2D033DA9}"/>
+    <hyperlink ref="G31" r:id="rId163" xr:uid="{623D873A-9C9E-461F-8026-747AFA17D74B}"/>
+    <hyperlink ref="H31" r:id="rId164" xr:uid="{1E9A819E-8B50-4F2A-95DF-43798FFD14F0}"/>
+    <hyperlink ref="G32" r:id="rId165" xr:uid="{4AAD2563-8643-4B82-A282-64CC2236BC1B}"/>
+    <hyperlink ref="H32" r:id="rId166" xr:uid="{04F051DF-F77F-49FE-97AF-5FAC69595722}"/>
+    <hyperlink ref="I32" r:id="rId167" xr:uid="{B442999A-F678-41FA-9495-342FBAB0DCDE}"/>
+    <hyperlink ref="I33" r:id="rId168" xr:uid="{130A8142-F9DA-47FA-914A-B6897F67F63A}"/>
+    <hyperlink ref="H33" r:id="rId169" xr:uid="{93B42705-7B49-44D7-86D0-9C78DE7C6078}"/>
+    <hyperlink ref="F35" r:id="rId170" xr:uid="{75C5445A-B974-473C-A5D5-8CEBCD47C527}"/>
+    <hyperlink ref="D35" r:id="rId171" xr:uid="{FCFAB579-F316-4C07-8961-81A5BEC47514}"/>
+    <hyperlink ref="I35" r:id="rId172" xr:uid="{7549FBC2-3EAF-491C-8850-8EA14D56B640}"/>
+    <hyperlink ref="H35" r:id="rId173" xr:uid="{EB31C25E-E7B7-4B6F-A735-6BE632CB4E74}"/>
+    <hyperlink ref="D37" r:id="rId174" xr:uid="{72D1A7E7-C5AA-4CA3-9B22-26DC18483425}"/>
+    <hyperlink ref="F37" r:id="rId175" xr:uid="{02CC40E4-1FB3-4A5C-959D-56A3B0A0677C}"/>
+    <hyperlink ref="G37" r:id="rId176" xr:uid="{F3F53B72-1272-4115-A7A4-89BA656B805B}"/>
+    <hyperlink ref="H37" r:id="rId177" xr:uid="{76961B16-2EA5-4184-8AFA-275E8CE35FE4}"/>
+    <hyperlink ref="I37" r:id="rId178" xr:uid="{CB235A1A-C954-4F96-937F-814677098B29}"/>
+    <hyperlink ref="D38" r:id="rId179" xr:uid="{11A09FE2-20C9-41AA-AD44-53BE500F21E4}"/>
+    <hyperlink ref="F38" r:id="rId180" xr:uid="{7DF4483B-7F73-40EE-8988-BEAB2B0FD71E}"/>
+    <hyperlink ref="G38" r:id="rId181" xr:uid="{2521C9FE-E2BF-4B66-B194-E41EEDE7AF62}"/>
+    <hyperlink ref="H38" r:id="rId182" xr:uid="{6C4A6C8E-3141-48C2-BB74-B7BD61AFAF5E}"/>
+    <hyperlink ref="I38" r:id="rId183" xr:uid="{18CE8D40-089B-4773-B2BD-D4A5CE8850D8}"/>
+    <hyperlink ref="G39" r:id="rId184" xr:uid="{F8FB4E8B-F1FF-4911-83C1-04532982FBDB}"/>
+    <hyperlink ref="H39" r:id="rId185" xr:uid="{038254BE-75B5-4348-8CEA-E772FEF55690}"/>
+    <hyperlink ref="G40" r:id="rId186" xr:uid="{A7335D22-114B-49B3-B160-4C0E27C63EF3}"/>
+    <hyperlink ref="H40" r:id="rId187" xr:uid="{6810003A-CF94-4BF1-9EFB-CE3D245B8D71}"/>
+    <hyperlink ref="I40" r:id="rId188" xr:uid="{E6903362-2190-4037-AC0D-EAF0CD36422D}"/>
+    <hyperlink ref="J40" r:id="rId189" xr:uid="{D7EB4DAC-1509-4AC6-8555-4907188F0758}"/>
+    <hyperlink ref="G41" r:id="rId190" xr:uid="{E3E3A292-EC3B-468B-9AFE-5868E722CA52}"/>
+    <hyperlink ref="H41" r:id="rId191" xr:uid="{0333FD81-9F44-4B2B-B06B-8B657DF05FEB}"/>
+    <hyperlink ref="G42" r:id="rId192" xr:uid="{9A8B2004-86C3-4F07-94D4-87629838F880}"/>
+    <hyperlink ref="H42" r:id="rId193" xr:uid="{817A7732-96FF-46B0-9569-6C60AFACE939}"/>
+    <hyperlink ref="G43" r:id="rId194" xr:uid="{FDB0C7F5-0A6B-4A7A-A09A-5E3EF5348AC6}"/>
+    <hyperlink ref="H43" r:id="rId195" xr:uid="{FE9B4741-3916-43EB-8EF7-1D0AEE7D2636}"/>
+    <hyperlink ref="I43" r:id="rId196" xr:uid="{0BFFF36A-70AD-460A-9F69-A45E3B1362AA}"/>
+    <hyperlink ref="G44" r:id="rId197" xr:uid="{F3414BD8-4E08-4A3D-BF3D-947B226A5123}"/>
+    <hyperlink ref="H44" r:id="rId198" xr:uid="{C3E7FC4C-298C-4EF7-A412-7DA406F09A81}"/>
+    <hyperlink ref="I44" r:id="rId199" xr:uid="{C4E23EE7-875D-4A6C-8D54-10AEA462C53A}"/>
+    <hyperlink ref="F44" r:id="rId200" xr:uid="{1AAAE983-E84A-4BCD-A6A8-BBDD8FFC74B2}"/>
+    <hyperlink ref="G45" r:id="rId201" xr:uid="{8C488E52-5A3A-424A-AE8F-930375EFDF31}"/>
+    <hyperlink ref="H45" r:id="rId202" xr:uid="{5DDE8498-5211-4866-B09B-6F58B1E93771}"/>
+    <hyperlink ref="I45" r:id="rId203" xr:uid="{18FE97B2-96D7-4131-A2EC-6FFC0C091D11}"/>
+    <hyperlink ref="G46" r:id="rId204" xr:uid="{0A1B6603-490C-4C47-AD7E-B5929AB5C158}"/>
+    <hyperlink ref="H46" r:id="rId205" xr:uid="{5B30F080-EAEA-4012-90B6-5C4696EB91C4}"/>
+    <hyperlink ref="G49" r:id="rId206" xr:uid="{1EC61023-C1BA-45FE-8448-A2F2D99E5675}"/>
+    <hyperlink ref="H49" r:id="rId207" xr:uid="{CAC3F4CA-2B81-427C-94AF-33C8A931FA78}"/>
+    <hyperlink ref="F49" r:id="rId208" xr:uid="{75BF41A5-6B20-4B2B-83AB-93126A4DEFD1}"/>
+    <hyperlink ref="D49" r:id="rId209" xr:uid="{3077A2E4-6FCF-4FDE-877E-6BE59D576A6D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
